--- a/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0206</v>
+        <v>0.031</v>
       </c>
       <c r="E2">
-        <v>0.00458</v>
+        <v>0.02905</v>
       </c>
       <c r="F2">
-        <v>0.0205</v>
+        <v>0.079</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0003108302770287232</v>
+        <v>0.0003711266341162705</v>
       </c>
       <c r="J2">
-        <v>0.0002537192326658555</v>
+        <v>0.0003064865607299795</v>
       </c>
       <c r="K2">
-        <v>5240.8</v>
+        <v>5701.1</v>
       </c>
       <c r="L2">
-        <v>0.2956310816527993</v>
+        <v>0.3304123561969342</v>
       </c>
       <c r="M2">
-        <v>1565.68</v>
+        <v>3065.63</v>
       </c>
       <c r="N2">
-        <v>0.02877977136911994</v>
+        <v>0.0573835484384213</v>
       </c>
       <c r="O2">
-        <v>0.2987482827049305</v>
+        <v>0.5377260528669906</v>
       </c>
       <c r="P2">
-        <v>1565.68</v>
+        <v>3065.63</v>
       </c>
       <c r="Q2">
-        <v>0.02877977136911994</v>
+        <v>0.0573835484384213</v>
       </c>
       <c r="R2">
-        <v>0.2987482827049305</v>
+        <v>0.5377260528669906</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7800.497</v>
+        <v>6372.031</v>
       </c>
       <c r="V2">
-        <v>0.1433859538510462</v>
+        <v>0.1192739337557442</v>
       </c>
       <c r="W2">
-        <v>0.06296594801531331</v>
+        <v>0.08148341225364555</v>
       </c>
       <c r="X2">
-        <v>0.07494084660409538</v>
+        <v>0.1073264734706174</v>
       </c>
       <c r="Y2">
-        <v>-0.01197489858878206</v>
+        <v>-0.02584306121697187</v>
       </c>
       <c r="Z2">
-        <v>0.1675041578791417</v>
+        <v>0.1538504735987216</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05285475936526891</v>
+        <v>0.08287869426671603</v>
       </c>
       <c r="AC2">
-        <v>-0.05285475936526891</v>
+        <v>-0.08287869426671603</v>
       </c>
       <c r="AD2">
-        <v>46215.4</v>
+        <v>48609.5</v>
       </c>
       <c r="AE2">
-        <v>10.69878131986655</v>
+        <v>14.05197745820406</v>
       </c>
       <c r="AF2">
-        <v>46226.09878131987</v>
+        <v>48623.55197745821</v>
       </c>
       <c r="AG2">
-        <v>38425.60178131986</v>
+        <v>42251.5209774582</v>
       </c>
       <c r="AH2">
-        <v>0.4593751984150695</v>
+        <v>0.4764816918787518</v>
       </c>
       <c r="AI2">
-        <v>0.3772706028195425</v>
+        <v>0.4091649896504599</v>
       </c>
       <c r="AJ2">
-        <v>0.4139454176280428</v>
+        <v>0.4416149643428142</v>
       </c>
       <c r="AK2">
-        <v>0.334930175099733</v>
+        <v>0.3756892258540793</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>6041.228758169936</v>
+        <v>5275.613197308444</v>
       </c>
       <c r="AP2">
-        <v>5022.954481218283</v>
+        <v>4585.578573633406</v>
       </c>
     </row>
     <row r="3">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05429999999999999</v>
+        <v>0.0386</v>
       </c>
       <c r="E3">
-        <v>0.05980000000000001</v>
+        <v>0.0423</v>
       </c>
       <c r="F3">
-        <v>-0.013</v>
+        <v>0.0327</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>197.1</v>
+        <v>191.1</v>
       </c>
       <c r="L3">
-        <v>0.4015074353228764</v>
+        <v>0.4110561411056141</v>
       </c>
       <c r="M3">
-        <v>150</v>
+        <v>151.7</v>
       </c>
       <c r="N3">
-        <v>0.06508721687060662</v>
+        <v>0.06599095180093961</v>
       </c>
       <c r="O3">
-        <v>0.7610350076103501</v>
+        <v>0.793825222396651</v>
       </c>
       <c r="P3">
-        <v>150</v>
+        <v>151.7</v>
       </c>
       <c r="Q3">
-        <v>0.06508721687060662</v>
+        <v>0.06599095180093961</v>
       </c>
       <c r="R3">
-        <v>0.7610350076103501</v>
+        <v>0.793825222396651</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>31.3</v>
+        <v>26</v>
       </c>
       <c r="V3">
-        <v>0.01358153258699991</v>
+        <v>0.01131024882547416</v>
       </c>
       <c r="W3">
-        <v>0.1644692923898531</v>
+        <v>0.1630546075085324</v>
       </c>
       <c r="X3">
-        <v>0.05602648992739939</v>
+        <v>0.08448397676705702</v>
       </c>
       <c r="Y3">
-        <v>0.1084428024624537</v>
+        <v>0.07857063074147541</v>
       </c>
       <c r="Z3">
-        <v>0.2694883618796662</v>
+        <v>0.2532548891431062</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04989109421838817</v>
+        <v>0.07857959369444978</v>
       </c>
       <c r="AC3">
-        <v>-0.04989109421838817</v>
+        <v>-0.07857959369444978</v>
       </c>
       <c r="AD3">
-        <v>695</v>
+        <v>540.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>695</v>
+        <v>540.9</v>
       </c>
       <c r="AG3">
-        <v>663.7</v>
+        <v>514.9</v>
       </c>
       <c r="AH3">
-        <v>0.2316975596746233</v>
+        <v>0.190477867380357</v>
       </c>
       <c r="AI3">
-        <v>0.3722150814053127</v>
+        <v>0.3322889789900479</v>
       </c>
       <c r="AJ3">
-        <v>0.2235959977091264</v>
+        <v>0.1829974766321925</v>
       </c>
       <c r="AK3">
-        <v>0.3615120649272836</v>
+        <v>0.3214508677737545</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Siam Commercial Bank Public Company Limited (SET:SCB)</t>
+          <t>LH Financial Group Public Company Limited (SET:LHFG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00814</v>
+        <v>-0.0499</v>
       </c>
       <c r="E4">
-        <v>-0.0688</v>
-      </c>
-      <c r="F4">
-        <v>-0.044</v>
+        <v>-0.192</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,28 +862,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>972.2</v>
+        <v>22.8</v>
       </c>
       <c r="L4">
-        <v>0.316760067770103</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="M4">
-        <v>452.9</v>
+        <v>14.6</v>
       </c>
       <c r="N4">
-        <v>0.03498729209637921</v>
+        <v>0.01937110256070054</v>
       </c>
       <c r="O4">
-        <v>0.4658506480148117</v>
+        <v>0.6403508771929824</v>
       </c>
       <c r="P4">
-        <v>452.9</v>
+        <v>14.6</v>
       </c>
       <c r="Q4">
-        <v>0.03498729209637921</v>
+        <v>0.01937110256070054</v>
       </c>
       <c r="R4">
-        <v>0.4658506480148117</v>
+        <v>0.6403508771929824</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,55 +892,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1290.2</v>
+        <v>15.7</v>
       </c>
       <c r="V4">
-        <v>0.09967013526771575</v>
+        <v>0.0208305691919862</v>
       </c>
       <c r="W4">
-        <v>0.07558758814794082</v>
+        <v>0.01996497373029773</v>
       </c>
       <c r="X4">
-        <v>0.05725860106978483</v>
+        <v>0.1061352848748142</v>
       </c>
       <c r="Y4">
-        <v>0.01832898707815599</v>
+        <v>-0.08617031114451644</v>
       </c>
       <c r="Z4">
-        <v>0.1919161601760836</v>
+        <v>0.0625</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05128914670278419</v>
+        <v>0.08063565439725519</v>
       </c>
       <c r="AC4">
-        <v>-0.05128914670278419</v>
+        <v>-0.08063565439725519</v>
       </c>
       <c r="AD4">
-        <v>4508.4</v>
+        <v>707.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4508.4</v>
+        <v>707.9</v>
       </c>
       <c r="AG4">
-        <v>3218.2</v>
+        <v>692.1999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.2583151417226739</v>
+        <v>0.4843322386425835</v>
       </c>
       <c r="AI4">
-        <v>0.261881803501516</v>
+        <v>0.4270117022560019</v>
       </c>
       <c r="AJ4">
-        <v>0.1991103081748943</v>
+        <v>0.4787329690849989</v>
       </c>
       <c r="AK4">
-        <v>0.2020822344460352</v>
+        <v>0.4215334023506486</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LH Financial Group Public Company Limited (SET:LHFG)</t>
+          <t>Thanachart Capital Public Company Limited (SET:TCAP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,10 +966,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00705</v>
+        <v>-0.211</v>
       </c>
       <c r="E5">
-        <v>-0.0499</v>
+        <v>-0.0267</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,34 +978,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.007233178997450496</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.006493229198555983</v>
       </c>
       <c r="K5">
-        <v>58.3</v>
+        <v>156.4</v>
       </c>
       <c r="L5">
-        <v>0.3550548112058465</v>
+        <v>0.5227272727272728</v>
       </c>
       <c r="M5">
-        <v>33.8</v>
+        <v>50</v>
       </c>
       <c r="N5">
-        <v>0.03941690962099125</v>
+        <v>0.03878374185541421</v>
       </c>
       <c r="O5">
-        <v>0.5797598627787307</v>
+        <v>0.319693094629156</v>
       </c>
       <c r="P5">
-        <v>33.8</v>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <v>0.03941690962099125</v>
+        <v>0.03878374185541421</v>
       </c>
       <c r="R5">
-        <v>0.5797598627787307</v>
+        <v>0.319693094629156</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,61 +1014,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>19</v>
+        <v>0.231</v>
       </c>
       <c r="V5">
-        <v>0.02215743440233236</v>
+        <v>0.0001791808873720137</v>
       </c>
       <c r="W5">
-        <v>0.04766576731256643</v>
+        <v>0.08297962648556877</v>
       </c>
       <c r="X5">
-        <v>0.07150545986378733</v>
+        <v>0.1182829569158142</v>
       </c>
       <c r="Y5">
-        <v>-0.0238396925512209</v>
+        <v>-0.03530333043024544</v>
       </c>
       <c r="Z5">
-        <v>0.08132336189391312</v>
+        <v>0.08818320932625012</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.0005725937896195816</v>
       </c>
       <c r="AB5">
-        <v>0.05176576428755306</v>
+        <v>0.08124614805762118</v>
       </c>
       <c r="AC5">
-        <v>-0.05176576428755306</v>
+        <v>-0.08067355426800159</v>
       </c>
       <c r="AD5">
-        <v>761.8</v>
+        <v>1713.4</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>6.629164219814058</v>
       </c>
       <c r="AF5">
-        <v>761.8</v>
+        <v>1720.029164219814</v>
       </c>
       <c r="AG5">
-        <v>742.8</v>
+        <v>1719.798164219814</v>
       </c>
       <c r="AH5">
-        <v>0.4704501945285</v>
+        <v>0.5715846385749609</v>
       </c>
       <c r="AI5">
-        <v>0.4001470742725076</v>
+        <v>0.4599218543659437</v>
       </c>
       <c r="AJ5">
-        <v>0.4641629694432294</v>
+        <v>0.5715517492400102</v>
       </c>
       <c r="AK5">
-        <v>0.3941001697792869</v>
+        <v>0.4598884930136906</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>490.945558739255</v>
+      </c>
+      <c r="AP5">
+        <v>492.7788436159926</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thanachart Capital Public Company Limited (SET:TCAP)</t>
+          <t>SCB X Public Company Limited (SET:SCB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,10 +1094,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.222</v>
+        <v>0.013</v>
       </c>
       <c r="E6">
-        <v>-0.0584</v>
+        <v>-0.00483</v>
+      </c>
+      <c r="F6">
+        <v>0.00198</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,34 +1109,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.004087766477475112</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.003607361947036004</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>125</v>
+        <v>1206.9</v>
       </c>
       <c r="L6">
-        <v>0.4437344692935747</v>
+        <v>0.3716740576496674</v>
       </c>
       <c r="M6">
-        <v>93.5</v>
+        <v>1853</v>
       </c>
       <c r="N6">
-        <v>0.07877664504170527</v>
+        <v>0.1762982132323559</v>
       </c>
       <c r="O6">
-        <v>0.748</v>
+        <v>1.535338470461513</v>
       </c>
       <c r="P6">
-        <v>93.5</v>
+        <v>1853</v>
       </c>
       <c r="Q6">
-        <v>0.07877664504170527</v>
+        <v>0.1762982132323559</v>
       </c>
       <c r="R6">
-        <v>0.748</v>
+        <v>1.535338470461513</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,67 +1145,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.197</v>
+        <v>1175.4</v>
       </c>
       <c r="V6">
-        <v>0.0001659785997135395</v>
+        <v>0.1118299621334653</v>
       </c>
       <c r="W6">
-        <v>0.06296594801531331</v>
+        <v>0.09528659403126481</v>
       </c>
       <c r="X6">
-        <v>0.08148072467811103</v>
+        <v>0.09028364158901601</v>
       </c>
       <c r="Y6">
-        <v>-0.01851477666279772</v>
+        <v>0.005002952442248798</v>
       </c>
       <c r="Z6">
-        <v>0.07735206328078352</v>
+        <v>0.204429558932776</v>
       </c>
       <c r="AA6">
-        <v>0.0002790368896038195</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05245951876877984</v>
+        <v>0.08116341716643918</v>
       </c>
       <c r="AC6">
-        <v>-0.05218048187917602</v>
+        <v>-0.08116341716643918</v>
       </c>
       <c r="AD6">
-        <v>1501.7</v>
+        <v>4455</v>
       </c>
       <c r="AE6">
-        <v>1.592380916476305</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1503.292380916476</v>
+        <v>4455</v>
       </c>
       <c r="AG6">
-        <v>1503.095380916476</v>
+        <v>3279.6</v>
       </c>
       <c r="AH6">
-        <v>0.5588047871893627</v>
+        <v>0.2976826856257016</v>
       </c>
       <c r="AI6">
-        <v>0.4120311142156914</v>
+        <v>0.2943722371629256</v>
       </c>
       <c r="AJ6">
-        <v>0.558772476555099</v>
+        <v>0.2378210613334107</v>
       </c>
       <c r="AK6">
-        <v>0.4119993651771937</v>
+        <v>0.2349536124941792</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1021.56462585034</v>
-      </c>
-      <c r="AP6">
-        <v>1022.513864569032</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
+          <t>Kiatnakin Phatra Bank Public Company Limited (SET:KKP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,10 +1219,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0498</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="E7">
-        <v>0.076</v>
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.059</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,28 +1240,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>915.9</v>
+        <v>217.1</v>
       </c>
       <c r="L7">
-        <v>0.3514042357274401</v>
+        <v>0.371492128678987</v>
       </c>
       <c r="M7">
-        <v>164.1</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N7">
-        <v>0.02095865741982451</v>
+        <v>0.04904511486299474</v>
       </c>
       <c r="O7">
-        <v>0.1791680314444808</v>
+        <v>0.4081068631966835</v>
       </c>
       <c r="P7">
-        <v>164.1</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.02095865741982451</v>
+        <v>0.04904511486299474</v>
       </c>
       <c r="R7">
-        <v>0.1791680314444808</v>
+        <v>0.4081068631966835</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1267,55 +1270,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>796.5</v>
+        <v>29.5</v>
       </c>
       <c r="V7">
-        <v>0.1017280355569179</v>
+        <v>0.01632991973429283</v>
       </c>
       <c r="W7">
-        <v>0.1016909633939179</v>
+        <v>0.1491378718142474</v>
       </c>
       <c r="X7">
-        <v>0.06442579576184326</v>
+        <v>0.1252125029005374</v>
       </c>
       <c r="Y7">
-        <v>0.03726516763207459</v>
+        <v>0.02392536891371003</v>
       </c>
       <c r="Z7">
-        <v>0.1885239379977288</v>
+        <v>0.1581596752368065</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05283855704780699</v>
+        <v>0.08151000663591526</v>
       </c>
       <c r="AC7">
-        <v>-0.05283855704780699</v>
+        <v>-0.08151000663591526</v>
       </c>
       <c r="AD7">
-        <v>4854.4</v>
+        <v>2817.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4854.4</v>
+        <v>2817.2</v>
       </c>
       <c r="AG7">
-        <v>4057.9</v>
+        <v>2787.7</v>
       </c>
       <c r="AH7">
-        <v>0.3827153680592238</v>
+        <v>0.6092955857862751</v>
       </c>
       <c r="AI7">
-        <v>0.3440396881644224</v>
+        <v>0.6645907053550365</v>
       </c>
       <c r="AJ7">
-        <v>0.3413556983747771</v>
+        <v>0.6067868181620304</v>
       </c>
       <c r="AK7">
-        <v>0.3047958838772674</v>
+        <v>0.6622401710416914</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1332,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kiatnakin Phatra Bank Public Company Limited (SET:KKP)</t>
+          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1341,13 +1344,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0397</v>
+        <v>0.0299</v>
       </c>
       <c r="E8">
-        <v>0.0126</v>
-      </c>
-      <c r="F8">
-        <v>0.016</v>
+        <v>0.0554</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1362,82 +1362,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>160.7</v>
+        <v>787</v>
       </c>
       <c r="L8">
-        <v>0.3280261277811798</v>
+        <v>0.3401625172890733</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>165.6</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.02530871744712068</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.2104193138500635</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>165.6</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.02530871744712068</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2104193138500635</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>33.7</v>
+        <v>714.8</v>
       </c>
       <c r="V8">
-        <v>0.02221489782465393</v>
+        <v>0.1092431837632962</v>
       </c>
       <c r="W8">
-        <v>0.1128035939912958</v>
+        <v>0.08521281548772697</v>
       </c>
       <c r="X8">
-        <v>0.08918031172410056</v>
+        <v>0.09639787691562758</v>
       </c>
       <c r="Y8">
-        <v>0.02362328226719525</v>
+        <v>-0.01118506142790061</v>
       </c>
       <c r="Z8">
-        <v>0.1634525557186708</v>
+        <v>0.1740386351326954</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05285475936526891</v>
+        <v>0.08287869426671603</v>
       </c>
       <c r="AC8">
-        <v>-0.05285475936526891</v>
+        <v>-0.08287869426671603</v>
       </c>
       <c r="AD8">
-        <v>2364.2</v>
+        <v>4074.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2364.2</v>
+        <v>4074.1</v>
       </c>
       <c r="AG8">
-        <v>2330.5</v>
+        <v>3359.3</v>
       </c>
       <c r="AH8">
-        <v>0.6091415026280531</v>
+        <v>0.3837227920469423</v>
       </c>
       <c r="AI8">
-        <v>0.6183663327491957</v>
+        <v>0.3152327821666499</v>
       </c>
       <c r="AJ8">
-        <v>0.6057179987004548</v>
+        <v>0.3392375662711437</v>
       </c>
       <c r="AK8">
-        <v>0.6149725564703399</v>
+        <v>0.2751427190748036</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1463,13 +1466,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.08779999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="E9">
-        <v>0.00458</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="F9">
-        <v>0.128</v>
+        <v>0.142</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1484,28 +1487,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>265</v>
+        <v>348.3</v>
       </c>
       <c r="L9">
-        <v>0.2147487844408428</v>
+        <v>0.2861015278462297</v>
       </c>
       <c r="M9">
-        <v>129.6</v>
+        <v>148.4</v>
       </c>
       <c r="N9">
-        <v>0.03043110735418427</v>
+        <v>0.03759531831885086</v>
       </c>
       <c r="O9">
-        <v>0.4890566037735849</v>
+        <v>0.4260694803330462</v>
       </c>
       <c r="P9">
-        <v>129.6</v>
+        <v>148.4</v>
       </c>
       <c r="Q9">
-        <v>0.03043110735418427</v>
+        <v>0.03759531831885086</v>
       </c>
       <c r="R9">
-        <v>0.4890566037735849</v>
+        <v>0.4260694803330462</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,55 +1517,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>437.5</v>
+        <v>401.5</v>
       </c>
       <c r="V9">
-        <v>0.1027284681130835</v>
+        <v>0.1017150963950042</v>
       </c>
       <c r="W9">
-        <v>0.04124449424911674</v>
+        <v>0.05633552227218322</v>
       </c>
       <c r="X9">
-        <v>0.06579800577427919</v>
+        <v>0.09598745376138404</v>
       </c>
       <c r="Y9">
-        <v>-0.02455351152516245</v>
+        <v>-0.03965193148920082</v>
       </c>
       <c r="Z9">
-        <v>0.134950405179296</v>
+        <v>0.1414413681727876</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05369211277201193</v>
+        <v>0.08401525667871815</v>
       </c>
       <c r="AC9">
-        <v>-0.05369211277201193</v>
+        <v>-0.08401525667871815</v>
       </c>
       <c r="AD9">
-        <v>2862</v>
+        <v>2405.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2862</v>
+        <v>2405.1</v>
       </c>
       <c r="AG9">
-        <v>2424.5</v>
+        <v>2003.6</v>
       </c>
       <c r="AH9">
-        <v>0.4019211324570273</v>
+        <v>0.3786128077576979</v>
       </c>
       <c r="AI9">
-        <v>0.316410914075974</v>
+        <v>0.2971790784742558</v>
       </c>
       <c r="AJ9">
-        <v>0.3627698891266291</v>
+        <v>0.3366885681157472</v>
       </c>
       <c r="AK9">
-        <v>0.2816664149540528</v>
+        <v>0.260491965260804</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1579,7 +1582,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
+          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,13 +1591,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0206</v>
+        <v>0.031</v>
       </c>
       <c r="E10">
-        <v>0.0318</v>
+        <v>-0.0307</v>
       </c>
       <c r="F10">
-        <v>0.109</v>
+        <v>0.095</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1609,28 +1612,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1231.6</v>
+        <v>743.3</v>
       </c>
       <c r="L10">
-        <v>0.3227125039304056</v>
+        <v>0.268319976896975</v>
       </c>
       <c r="M10">
-        <v>223.6</v>
+        <v>202.2</v>
       </c>
       <c r="N10">
-        <v>0.02216494845360825</v>
+        <v>0.02474181391023445</v>
       </c>
       <c r="O10">
-        <v>0.181552452094836</v>
+        <v>0.2720301358805328</v>
       </c>
       <c r="P10">
-        <v>223.6</v>
+        <v>202.2</v>
       </c>
       <c r="Q10">
-        <v>0.02216494845360825</v>
+        <v>0.02474181391023445</v>
       </c>
       <c r="R10">
-        <v>0.181552452094836</v>
+        <v>0.2720301358805328</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1639,55 +1642,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1577.9</v>
+        <v>1163.8</v>
       </c>
       <c r="V10">
-        <v>0.156413560666138</v>
+        <v>0.1424061475209241</v>
       </c>
       <c r="W10">
-        <v>0.09515494742372382</v>
+        <v>0.05132684698619636</v>
       </c>
       <c r="X10">
-        <v>0.07494084660409538</v>
+        <v>0.1100931073693448</v>
       </c>
       <c r="Y10">
-        <v>0.02021410081962845</v>
+        <v>-0.05876626038314844</v>
       </c>
       <c r="Z10">
-        <v>0.2034046454116167</v>
+        <v>0.1371834361722147</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05435683469659256</v>
+        <v>0.08482627846663103</v>
       </c>
       <c r="AC10">
-        <v>-0.05435683469659256</v>
+        <v>-0.08482627846663103</v>
       </c>
       <c r="AD10">
-        <v>10276</v>
+        <v>8727.4</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>10276</v>
+        <v>8727.4</v>
       </c>
       <c r="AG10">
-        <v>8698.1</v>
+        <v>7563.599999999999</v>
       </c>
       <c r="AH10">
-        <v>0.5046159890001964</v>
+        <v>0.5164203126664221</v>
       </c>
       <c r="AI10">
-        <v>0.3982544394750917</v>
+        <v>0.3915317804974338</v>
       </c>
       <c r="AJ10">
-        <v>0.4630072234258308</v>
+        <v>0.4806558210472801</v>
       </c>
       <c r="AK10">
-        <v>0.3590591421152791</v>
+        <v>0.3580131208997188</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1704,7 +1707,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
+          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1713,13 +1716,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0167</v>
+        <v>0.0138</v>
       </c>
       <c r="E11">
-        <v>-0.06269999999999999</v>
+        <v>0.0179</v>
       </c>
       <c r="F11">
-        <v>0.0205</v>
+        <v>0.079</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1734,28 +1737,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>671.8</v>
+        <v>1125.4</v>
       </c>
       <c r="L11">
-        <v>0.2339543792442974</v>
+        <v>0.3327321645034444</v>
       </c>
       <c r="M11">
-        <v>198.7</v>
+        <v>227.5</v>
       </c>
       <c r="N11">
-        <v>0.02857348288754673</v>
+        <v>0.02250336313998575</v>
       </c>
       <c r="O11">
-        <v>0.2957725513545698</v>
+        <v>0.2021503465434512</v>
       </c>
       <c r="P11">
-        <v>198.7</v>
+        <v>227.5</v>
       </c>
       <c r="Q11">
-        <v>0.02857348288754673</v>
+        <v>0.02250336313998575</v>
       </c>
       <c r="R11">
-        <v>0.2957725513545698</v>
+        <v>0.2021503465434512</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1764,55 +1767,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1902.1</v>
+        <v>1354.2</v>
       </c>
       <c r="V11">
-        <v>0.2735260281852172</v>
+        <v>0.1339518873150273</v>
       </c>
       <c r="W11">
-        <v>0.04826773577043008</v>
+        <v>0.08148341225364555</v>
       </c>
       <c r="X11">
-        <v>0.07695198627734527</v>
+        <v>0.1073264734706174</v>
       </c>
       <c r="Y11">
-        <v>-0.02868425050691519</v>
+        <v>-0.02584306121697187</v>
       </c>
       <c r="Z11">
-        <v>0.1494802159303276</v>
+        <v>0.1502610009107266</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05458139723360484</v>
+        <v>0.08525504687432837</v>
       </c>
       <c r="AC11">
-        <v>-0.05458139723360484</v>
+        <v>-0.08525504687432837</v>
       </c>
       <c r="AD11">
-        <v>7613.8</v>
+        <v>9886.799999999999</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>7613.8</v>
+        <v>9886.799999999999</v>
       </c>
       <c r="AG11">
-        <v>5711.700000000001</v>
+        <v>8532.599999999999</v>
       </c>
       <c r="AH11">
-        <v>0.5226458353354659</v>
+        <v>0.4944289972194995</v>
       </c>
       <c r="AI11">
-        <v>0.3437722934106322</v>
+        <v>0.4009278258542243</v>
       </c>
       <c r="AJ11">
-        <v>0.4509580994339042</v>
+        <v>0.4577034899314458</v>
       </c>
       <c r="AK11">
-        <v>0.2821191660451355</v>
+        <v>0.3661180145544418</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1838,10 +1841,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0229</v>
+        <v>0.0312</v>
       </c>
       <c r="E12">
-        <v>-0.0867</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="F12">
         <v>0.098</v>
@@ -1853,34 +1856,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.001513498732756156</v>
+        <v>0.001490910416266843</v>
       </c>
       <c r="J12">
-        <v>0.001209356553660922</v>
+        <v>0.001205774639768358</v>
       </c>
       <c r="K12">
-        <v>597.7</v>
+        <v>808.9</v>
       </c>
       <c r="L12">
-        <v>0.2484619221815763</v>
+        <v>0.319281626208802</v>
       </c>
       <c r="M12">
-        <v>114.3</v>
+        <v>154.8</v>
       </c>
       <c r="N12">
-        <v>0.02066309928411309</v>
+        <v>0.02163189446765696</v>
       </c>
       <c r="O12">
-        <v>0.191233060063577</v>
+        <v>0.1913709976511312</v>
       </c>
       <c r="P12">
-        <v>114.3</v>
+        <v>154.8</v>
       </c>
       <c r="Q12">
-        <v>0.02066309928411309</v>
+        <v>0.02163189446765696</v>
       </c>
       <c r="R12">
-        <v>0.191233060063577</v>
+        <v>0.1913709976511312</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1889,55 +1892,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1687.5</v>
+        <v>1468.2</v>
       </c>
       <c r="V12">
-        <v>0.3050654421867091</v>
+        <v>0.2051676192339403</v>
       </c>
       <c r="W12">
-        <v>0.05570155818981586</v>
+        <v>0.07682299086367694</v>
       </c>
       <c r="X12">
-        <v>0.07937750421342943</v>
+        <v>0.1119478670956091</v>
       </c>
       <c r="Y12">
-        <v>-0.02367594602361357</v>
+        <v>-0.03512487623193215</v>
       </c>
       <c r="Z12">
-        <v>0.1745428038220292</v>
+        <v>0.1644259064944794</v>
       </c>
       <c r="AA12">
-        <v>0.0002110844836965236</v>
+        <v>0.0001982605881719666</v>
       </c>
       <c r="AB12">
-        <v>0.05566095710310674</v>
+        <v>0.086723775552905</v>
       </c>
       <c r="AC12">
-        <v>-0.05544987261941021</v>
+        <v>-0.08652551496473304</v>
       </c>
       <c r="AD12">
-        <v>6560.5</v>
+        <v>8068.7</v>
       </c>
       <c r="AE12">
-        <v>4.595637242408961</v>
+        <v>4.913892301939767</v>
       </c>
       <c r="AF12">
-        <v>6565.095637242409</v>
+        <v>8073.61389230194</v>
       </c>
       <c r="AG12">
-        <v>4877.595637242409</v>
+        <v>6605.41389230194</v>
       </c>
       <c r="AH12">
-        <v>0.5427180970834944</v>
+        <v>0.5301224927398573</v>
       </c>
       <c r="AI12">
-        <v>0.3753500322918374</v>
+        <v>0.4467492452883501</v>
       </c>
       <c r="AJ12">
-        <v>0.4685852593442633</v>
+        <v>0.4799918049711773</v>
       </c>
       <c r="AK12">
-        <v>0.3086481123196907</v>
+        <v>0.3978274942068498</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1946,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>1438.706140350877</v>
+        <v>1695.105042016807</v>
       </c>
       <c r="AP12">
-        <v>1069.648166061932</v>
+        <v>1387.69199418108</v>
       </c>
     </row>
     <row r="13">
@@ -1969,10 +1972,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0357</v>
-      </c>
-      <c r="E13">
-        <v>0.08800000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1981,34 +1981,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.002411311279152648</v>
+        <v>0.001426592014536894</v>
       </c>
       <c r="J13">
-        <v>0.001881898168120849</v>
+        <v>0.001180237798810699</v>
       </c>
       <c r="K13">
-        <v>45.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L13">
-        <v>0.1528384279475982</v>
+        <v>0.2898148148148149</v>
       </c>
       <c r="M13">
-        <v>5.18</v>
+        <v>9.23</v>
       </c>
       <c r="N13">
-        <v>0.005574088023243301</v>
+        <v>0.01103934936012439</v>
       </c>
       <c r="O13">
-        <v>0.1138461538461538</v>
+        <v>0.09829605963791267</v>
       </c>
       <c r="P13">
-        <v>5.18</v>
+        <v>9.23</v>
       </c>
       <c r="Q13">
-        <v>0.005574088023243301</v>
+        <v>0.01103934936012439</v>
       </c>
       <c r="R13">
-        <v>0.1138461538461538</v>
+        <v>0.09829605963791267</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2017,55 +2017,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>24.6</v>
+        <v>22.7</v>
       </c>
       <c r="V13">
-        <v>0.02647153771656086</v>
+        <v>0.02714986245664394</v>
       </c>
       <c r="W13">
-        <v>0.03455346294046173</v>
+        <v>0.07504795396419438</v>
       </c>
       <c r="X13">
-        <v>0.1679131430137221</v>
+        <v>0.2691089308540316</v>
       </c>
       <c r="Y13">
-        <v>-0.1333596800732604</v>
+        <v>-0.1940609768898372</v>
       </c>
       <c r="Z13">
-        <v>0.06420222756175233</v>
+        <v>0.05948546263498414</v>
       </c>
       <c r="AA13">
-        <v>0.0001208220544377396</v>
+        <v>7.020699148154979e-05</v>
       </c>
       <c r="AB13">
-        <v>0.05753511247810464</v>
+        <v>0.08858594024423891</v>
       </c>
       <c r="AC13">
-        <v>-0.0574142904236669</v>
+        <v>-0.08851573325275736</v>
       </c>
       <c r="AD13">
-        <v>4217.6</v>
+        <v>5213</v>
       </c>
       <c r="AE13">
-        <v>4.510763160981284</v>
+        <v>2.508920936450231</v>
       </c>
       <c r="AF13">
-        <v>4222.110763160982</v>
+        <v>5215.508920936451</v>
       </c>
       <c r="AG13">
-        <v>4197.510763160982</v>
+        <v>5192.808920936451</v>
       </c>
       <c r="AH13">
-        <v>0.819602815087926</v>
+        <v>0.8618383952228991</v>
       </c>
       <c r="AI13">
-        <v>0.771399788146252</v>
+        <v>0.8151259141738515</v>
       </c>
       <c r="AJ13">
-        <v>0.8187372144340604</v>
+        <v>0.8613181902455856</v>
       </c>
       <c r="AK13">
-        <v>0.7703676971698648</v>
+        <v>0.8144676906256475</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2074,10 +2074,10 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>2603.456790123457</v>
+        <v>5407.676348547718</v>
       </c>
       <c r="AP13">
-        <v>2591.056026642581</v>
+        <v>5386.7312457847</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.031</v>
+        <v>0.0352</v>
       </c>
       <c r="E2">
-        <v>0.02905</v>
+        <v>0.0147</v>
       </c>
       <c r="F2">
-        <v>0.079</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0003711266341162705</v>
+        <v>0.0003230734402049593</v>
       </c>
       <c r="J2">
-        <v>0.0003064865607299795</v>
+        <v>0.0002622246895760832</v>
       </c>
       <c r="K2">
-        <v>5701.1</v>
+        <v>6251.9</v>
       </c>
       <c r="L2">
-        <v>0.3304123561969342</v>
+        <v>0.3189663528991607</v>
       </c>
       <c r="M2">
-        <v>3065.63</v>
+        <v>2349.1</v>
       </c>
       <c r="N2">
-        <v>0.0573835484384213</v>
+        <v>0.04412615523330077</v>
       </c>
       <c r="O2">
-        <v>0.5377260528669906</v>
+        <v>0.3757417745005519</v>
       </c>
       <c r="P2">
-        <v>3065.63</v>
+        <v>2349.1</v>
       </c>
       <c r="Q2">
-        <v>0.0573835484384213</v>
+        <v>0.04412615523330077</v>
       </c>
       <c r="R2">
-        <v>0.5377260528669906</v>
+        <v>0.3757417745005519</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6372.031</v>
+        <v>5791.58</v>
       </c>
       <c r="V2">
-        <v>0.1192739337557442</v>
+        <v>0.1087906679690435</v>
       </c>
       <c r="W2">
-        <v>0.08148341225364555</v>
+        <v>0.08958797787135661</v>
       </c>
       <c r="X2">
-        <v>0.1073264734706174</v>
+        <v>0.08760496010773849</v>
       </c>
       <c r="Y2">
-        <v>-0.02584306121697187</v>
+        <v>0.001983017763618117</v>
       </c>
       <c r="Z2">
-        <v>0.1538504735987216</v>
+        <v>0.1754164423378456</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08287869426671603</v>
+        <v>0.07024146141119464</v>
       </c>
       <c r="AC2">
-        <v>-0.08287869426671603</v>
+        <v>-0.07024146141119464</v>
       </c>
       <c r="AD2">
-        <v>48609.5</v>
+        <v>47958.8</v>
       </c>
       <c r="AE2">
-        <v>14.05197745820406</v>
+        <v>14.53799517631348</v>
       </c>
       <c r="AF2">
-        <v>48623.55197745821</v>
+        <v>47973.33799517631</v>
       </c>
       <c r="AG2">
-        <v>42251.5209774582</v>
+        <v>42181.75799517631</v>
       </c>
       <c r="AH2">
-        <v>0.4764816918787518</v>
+        <v>0.4740011044975192</v>
       </c>
       <c r="AI2">
-        <v>0.4091649896504599</v>
+        <v>0.3812808105796283</v>
       </c>
       <c r="AJ2">
-        <v>0.4416149643428142</v>
+        <v>0.4420745035458572</v>
       </c>
       <c r="AK2">
-        <v>0.3756892258540793</v>
+        <v>0.3514269162442886</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>5275.613197308444</v>
+        <v>5190.346320346321</v>
       </c>
       <c r="AP2">
-        <v>4585.578573633406</v>
+        <v>4565.12532415328</v>
       </c>
     </row>
     <row r="3">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0386</v>
+        <v>0.0136</v>
       </c>
       <c r="E3">
-        <v>0.0423</v>
+        <v>0.0147</v>
       </c>
       <c r="F3">
-        <v>0.0327</v>
+        <v>0.0832</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>191.1</v>
+        <v>200.4</v>
       </c>
       <c r="L3">
-        <v>0.4110561411056141</v>
+        <v>0.3995215311004784</v>
       </c>
       <c r="M3">
-        <v>151.7</v>
+        <v>213.5</v>
       </c>
       <c r="N3">
-        <v>0.06599095180093961</v>
+        <v>0.09137598972822598</v>
       </c>
       <c r="O3">
-        <v>0.793825222396651</v>
+        <v>1.065369261477046</v>
       </c>
       <c r="P3">
-        <v>151.7</v>
+        <v>213.5</v>
       </c>
       <c r="Q3">
-        <v>0.06599095180093961</v>
+        <v>0.09137598972822598</v>
       </c>
       <c r="R3">
-        <v>0.793825222396651</v>
+        <v>1.065369261477046</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>26</v>
+        <v>21.8</v>
       </c>
       <c r="V3">
-        <v>0.01131024882547416</v>
+        <v>0.009330194735715815</v>
       </c>
       <c r="W3">
-        <v>0.1630546075085324</v>
+        <v>0.1843945528156055</v>
       </c>
       <c r="X3">
-        <v>0.08448397676705702</v>
+        <v>0.07125336447664697</v>
       </c>
       <c r="Y3">
-        <v>0.07857063074147541</v>
+        <v>0.1131411883389585</v>
       </c>
       <c r="Z3">
-        <v>0.2532548891431062</v>
+        <v>0.3131672597864769</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07857959369444978</v>
+        <v>0.06719656201234664</v>
       </c>
       <c r="AC3">
-        <v>-0.07857959369444978</v>
+        <v>-0.06719656201234664</v>
       </c>
       <c r="AD3">
-        <v>540.9</v>
+        <v>550.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>540.9</v>
+        <v>550.1</v>
       </c>
       <c r="AG3">
-        <v>514.9</v>
+        <v>528.3000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.190477867380357</v>
+        <v>0.1905702210212707</v>
       </c>
       <c r="AI3">
-        <v>0.3322889789900479</v>
+        <v>0.3319254208652628</v>
       </c>
       <c r="AJ3">
-        <v>0.1829974766321925</v>
+        <v>0.1844107791119799</v>
       </c>
       <c r="AK3">
-        <v>0.3214508677737545</v>
+        <v>0.3230204830327117</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LH Financial Group Public Company Limited (SET:LHFG)</t>
+          <t>Thanachart Capital Public Company Limited (SET:TCAP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0499</v>
+        <v>-0.216</v>
       </c>
       <c r="E4">
-        <v>-0.192</v>
+        <v>-0.0421</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.005947584898426812</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.005360689127052306</v>
       </c>
       <c r="K4">
-        <v>22.8</v>
+        <v>171.1</v>
       </c>
       <c r="L4">
-        <v>0.1935483870967742</v>
+        <v>0.5617202889034799</v>
       </c>
       <c r="M4">
-        <v>14.6</v>
+        <v>88.8</v>
       </c>
       <c r="N4">
-        <v>0.01937110256070054</v>
+        <v>0.05847876193612117</v>
       </c>
       <c r="O4">
-        <v>0.6403508771929824</v>
+        <v>0.5189947399181765</v>
       </c>
       <c r="P4">
-        <v>14.6</v>
+        <v>88.8</v>
       </c>
       <c r="Q4">
-        <v>0.01937110256070054</v>
+        <v>0.05847876193612117</v>
       </c>
       <c r="R4">
-        <v>0.6403508771929824</v>
+        <v>0.5189947399181765</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,61 +892,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>15.7</v>
+        <v>0.18</v>
       </c>
       <c r="V4">
-        <v>0.0208305691919862</v>
+        <v>0.000118538030951597</v>
       </c>
       <c r="W4">
-        <v>0.01996497373029773</v>
+        <v>0.09650310208685843</v>
       </c>
       <c r="X4">
-        <v>0.1061352848748142</v>
+        <v>0.09269070434888894</v>
       </c>
       <c r="Y4">
-        <v>-0.08617031114451644</v>
+        <v>0.003812397737969486</v>
       </c>
       <c r="Z4">
-        <v>0.0625</v>
+        <v>0.08723884625562078</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.0004676603345790941</v>
       </c>
       <c r="AB4">
-        <v>0.08063565439725519</v>
+        <v>0.06924021084811624</v>
       </c>
       <c r="AC4">
-        <v>-0.08063565439725519</v>
+        <v>-0.06877255051353715</v>
       </c>
       <c r="AD4">
-        <v>707.9</v>
+        <v>1842.1</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>5.391828199695965</v>
       </c>
       <c r="AF4">
-        <v>707.9</v>
+        <v>1847.491828199696</v>
       </c>
       <c r="AG4">
-        <v>692.1999999999999</v>
+        <v>1847.311828199696</v>
       </c>
       <c r="AH4">
-        <v>0.4843322386425835</v>
+        <v>0.548869968346842</v>
       </c>
       <c r="AI4">
-        <v>0.4270117022560019</v>
+        <v>0.4721430325730317</v>
       </c>
       <c r="AJ4">
-        <v>0.4787329690849989</v>
+        <v>0.5488458423974893</v>
       </c>
       <c r="AK4">
-        <v>0.4215334023506486</v>
+        <v>0.472118749714998</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>637.4048442906574</v>
+      </c>
+      <c r="AP4">
+        <v>639.2082450517978</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thanachart Capital Public Company Limited (SET:TCAP)</t>
+          <t>LH Financial Group Public Company Limited (SET:LHFG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,10 +972,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.211</v>
+        <v>-0.00305</v>
       </c>
       <c r="E5">
-        <v>-0.0267</v>
+        <v>-0.0751</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,34 +984,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.007233178997450496</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.006493229198555983</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>156.4</v>
+        <v>57.1</v>
       </c>
       <c r="L5">
-        <v>0.5227272727272728</v>
+        <v>0.3281609195402299</v>
       </c>
       <c r="M5">
-        <v>50</v>
+        <v>5.8</v>
       </c>
       <c r="N5">
-        <v>0.03878374185541421</v>
+        <v>0.009359367435856058</v>
       </c>
       <c r="O5">
-        <v>0.319693094629156</v>
+        <v>0.1015761821366025</v>
       </c>
       <c r="P5">
-        <v>50</v>
+        <v>5.8</v>
       </c>
       <c r="Q5">
-        <v>0.03878374185541421</v>
+        <v>0.009359367435856058</v>
       </c>
       <c r="R5">
-        <v>0.319693094629156</v>
+        <v>0.1015761821366025</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1014,67 +1020,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.231</v>
+        <v>16</v>
       </c>
       <c r="V5">
-        <v>0.0001791808873720137</v>
+        <v>0.0258189446506374</v>
       </c>
       <c r="W5">
-        <v>0.08297962648556877</v>
+        <v>0.06011159069375724</v>
       </c>
       <c r="X5">
-        <v>0.1182829569158142</v>
+        <v>0.08849668335293355</v>
       </c>
       <c r="Y5">
-        <v>-0.03530333043024544</v>
+        <v>-0.02838509265917631</v>
       </c>
       <c r="Z5">
-        <v>0.08818320932625012</v>
+        <v>0.1059618780829426</v>
       </c>
       <c r="AA5">
-        <v>0.0005725937896195816</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08124614805762118</v>
+        <v>0.06899624535735799</v>
       </c>
       <c r="AC5">
-        <v>-0.08067355426800159</v>
+        <v>-0.06899624535735799</v>
       </c>
       <c r="AD5">
-        <v>1713.4</v>
+        <v>635</v>
       </c>
       <c r="AE5">
-        <v>6.629164219814058</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1720.029164219814</v>
+        <v>635</v>
       </c>
       <c r="AG5">
-        <v>1719.798164219814</v>
+        <v>619</v>
       </c>
       <c r="AH5">
-        <v>0.5715846385749609</v>
+        <v>0.5060970749980075</v>
       </c>
       <c r="AI5">
-        <v>0.4599218543659437</v>
+        <v>0.3964290173554751</v>
       </c>
       <c r="AJ5">
-        <v>0.5715517492400102</v>
+        <v>0.4997174457092112</v>
       </c>
       <c r="AK5">
-        <v>0.4598884930136906</v>
+        <v>0.39033926094085</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>490.945558739255</v>
-      </c>
-      <c r="AP5">
-        <v>492.7788436159926</v>
       </c>
     </row>
     <row r="6">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.013</v>
+        <v>0.0156</v>
       </c>
       <c r="E6">
-        <v>-0.00483</v>
+        <v>-0.0122</v>
       </c>
       <c r="F6">
-        <v>0.00198</v>
+        <v>-0.053</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,28 +1115,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1206.9</v>
+        <v>1085</v>
       </c>
       <c r="L6">
-        <v>0.3716740576496674</v>
+        <v>0.316160615420479</v>
       </c>
       <c r="M6">
-        <v>1853</v>
+        <v>846.4</v>
       </c>
       <c r="N6">
-        <v>0.1762982132323559</v>
+        <v>0.08106115021788057</v>
       </c>
       <c r="O6">
-        <v>1.535338470461513</v>
+        <v>0.7800921658986175</v>
       </c>
       <c r="P6">
-        <v>1853</v>
+        <v>846.4</v>
       </c>
       <c r="Q6">
-        <v>0.1762982132323559</v>
+        <v>0.08106115021788057</v>
       </c>
       <c r="R6">
-        <v>1.535338470461513</v>
+        <v>0.7800921658986175</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1145,55 +1145,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1175.4</v>
+        <v>993.9</v>
       </c>
       <c r="V6">
-        <v>0.1118299621334653</v>
+        <v>0.09518747306421491</v>
       </c>
       <c r="W6">
-        <v>0.09528659403126481</v>
+        <v>0.08958797787135661</v>
       </c>
       <c r="X6">
-        <v>0.09028364158901601</v>
+        <v>0.07700508658276684</v>
       </c>
       <c r="Y6">
-        <v>0.005002952442248798</v>
+        <v>0.01258289128858978</v>
       </c>
       <c r="Z6">
-        <v>0.204429558932776</v>
+        <v>0.2205399430624193</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08116341716643918</v>
+        <v>0.06955473590073123</v>
       </c>
       <c r="AC6">
-        <v>-0.08116341716643918</v>
+        <v>-0.06955473590073123</v>
       </c>
       <c r="AD6">
-        <v>4455</v>
+        <v>5207.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4455</v>
+        <v>5207.2</v>
       </c>
       <c r="AG6">
-        <v>3279.6</v>
+        <v>4213.3</v>
       </c>
       <c r="AH6">
-        <v>0.2976826856257016</v>
+        <v>0.3327560755845533</v>
       </c>
       <c r="AI6">
-        <v>0.2943722371629256</v>
+        <v>0.2874650826423469</v>
       </c>
       <c r="AJ6">
-        <v>0.2378210613334107</v>
+        <v>0.2875030706662663</v>
       </c>
       <c r="AK6">
-        <v>0.2349536124941792</v>
+        <v>0.2460996594685841</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kiatnakin Phatra Bank Public Company Limited (SET:KKP)</t>
+          <t>TMBThanachart Bank Public Company Limited (SET:TTB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.07440000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E7">
-        <v>0.06849999999999999</v>
+        <v>0.07490000000000001</v>
       </c>
       <c r="F7">
-        <v>0.059</v>
+        <v>0.115</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1240,28 +1240,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>217.1</v>
+        <v>477.1</v>
       </c>
       <c r="L7">
-        <v>0.371492128678987</v>
+        <v>0.3304016620498615</v>
       </c>
       <c r="M7">
-        <v>88.59999999999999</v>
+        <v>140.3</v>
       </c>
       <c r="N7">
-        <v>0.04904511486299474</v>
+        <v>0.02957419898819562</v>
       </c>
       <c r="O7">
-        <v>0.4081068631966835</v>
+        <v>0.2940683294906728</v>
       </c>
       <c r="P7">
-        <v>88.59999999999999</v>
+        <v>140.3</v>
       </c>
       <c r="Q7">
-        <v>0.04904511486299474</v>
+        <v>0.02957419898819562</v>
       </c>
       <c r="R7">
-        <v>0.4081068631966835</v>
+        <v>0.2940683294906728</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,55 +1270,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>29.5</v>
+        <v>371.2</v>
       </c>
       <c r="V7">
-        <v>0.01632991973429283</v>
+        <v>0.07824620573355817</v>
       </c>
       <c r="W7">
-        <v>0.1491378718142474</v>
+        <v>0.08387834036568215</v>
       </c>
       <c r="X7">
-        <v>0.1252125029005374</v>
+        <v>0.07511071374149716</v>
       </c>
       <c r="Y7">
-        <v>0.02392536891371003</v>
+        <v>0.008767626624184982</v>
       </c>
       <c r="Z7">
-        <v>0.1581596752368065</v>
+        <v>0.1877372718290083</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08151000663591526</v>
+        <v>0.07006818447553556</v>
       </c>
       <c r="AC7">
-        <v>-0.08151000663591526</v>
+        <v>-0.07006818447553556</v>
       </c>
       <c r="AD7">
-        <v>2817.2</v>
+        <v>1954.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2817.2</v>
+        <v>1954.5</v>
       </c>
       <c r="AG7">
-        <v>2787.7</v>
+        <v>1583.3</v>
       </c>
       <c r="AH7">
-        <v>0.6092955857862751</v>
+        <v>0.2917817421810853</v>
       </c>
       <c r="AI7">
-        <v>0.6645907053550365</v>
+        <v>0.2421512996506182</v>
       </c>
       <c r="AJ7">
-        <v>0.6067868181620304</v>
+        <v>0.2502331168112781</v>
       </c>
       <c r="AK7">
-        <v>0.6622401710416914</v>
+        <v>0.2056180358951716</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
+          <t>Kiatnakin Phatra Bank Public Company Limited (SET:KKP)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0299</v>
+        <v>0.0725</v>
       </c>
       <c r="E8">
-        <v>0.0554</v>
+        <v>0.00942</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1362,28 +1362,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>787</v>
+        <v>169.7</v>
       </c>
       <c r="L8">
-        <v>0.3401625172890733</v>
+        <v>0.2666142969363708</v>
       </c>
       <c r="M8">
-        <v>165.6</v>
+        <v>63.7</v>
       </c>
       <c r="N8">
-        <v>0.02530871744712068</v>
+        <v>0.05117287917737789</v>
       </c>
       <c r="O8">
-        <v>0.2104193138500635</v>
+        <v>0.3753682969946965</v>
       </c>
       <c r="P8">
-        <v>165.6</v>
+        <v>63.7</v>
       </c>
       <c r="Q8">
-        <v>0.02530871744712068</v>
+        <v>0.05117287917737789</v>
       </c>
       <c r="R8">
-        <v>0.2104193138500635</v>
+        <v>0.3753682969946965</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1392,55 +1392,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>714.8</v>
+        <v>26.4</v>
       </c>
       <c r="V8">
-        <v>0.1092431837632962</v>
+        <v>0.02120822622107969</v>
       </c>
       <c r="W8">
-        <v>0.08521281548772697</v>
+        <v>0.1195744081172491</v>
       </c>
       <c r="X8">
-        <v>0.09639787691562758</v>
+        <v>0.1235387367767436</v>
       </c>
       <c r="Y8">
-        <v>-0.01118506142790061</v>
+        <v>-0.003964328659494476</v>
       </c>
       <c r="Z8">
-        <v>0.1740386351326954</v>
+        <v>0.1542768499890928</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08287869426671603</v>
+        <v>0.07024146141119464</v>
       </c>
       <c r="AC8">
-        <v>-0.08287869426671603</v>
+        <v>-0.07024146141119464</v>
       </c>
       <c r="AD8">
-        <v>4074.1</v>
+        <v>3272.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>4074.1</v>
+        <v>3272.1</v>
       </c>
       <c r="AG8">
-        <v>3359.3</v>
+        <v>3245.7</v>
       </c>
       <c r="AH8">
-        <v>0.3837227920469423</v>
+        <v>0.7244127609643782</v>
       </c>
       <c r="AI8">
-        <v>0.3152327821666499</v>
+        <v>0.6645072195934282</v>
       </c>
       <c r="AJ8">
-        <v>0.3392375662711437</v>
+        <v>0.7227925620754927</v>
       </c>
       <c r="AK8">
-        <v>0.2751427190748036</v>
+        <v>0.6626988178124426</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TMBThanachart Bank Public Company Limited (SET:TTB)</t>
+          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,13 +1466,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.104</v>
+        <v>0.0352</v>
       </c>
       <c r="E9">
-        <v>0.08939999999999999</v>
-      </c>
-      <c r="F9">
-        <v>0.142</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1487,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>348.3</v>
+        <v>891.4</v>
       </c>
       <c r="L9">
-        <v>0.2861015278462297</v>
+        <v>0.3343084308430843</v>
       </c>
       <c r="M9">
-        <v>148.4</v>
+        <v>172.6</v>
       </c>
       <c r="N9">
-        <v>0.03759531831885086</v>
+        <v>0.02839189367021977</v>
       </c>
       <c r="O9">
-        <v>0.4260694803330462</v>
+        <v>0.1936280008974647</v>
       </c>
       <c r="P9">
-        <v>148.4</v>
+        <v>172.6</v>
       </c>
       <c r="Q9">
-        <v>0.03759531831885086</v>
+        <v>0.02839189367021977</v>
       </c>
       <c r="R9">
-        <v>0.4260694803330462</v>
+        <v>0.1936280008974647</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1517,55 +1514,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>401.5</v>
+        <v>730.1</v>
       </c>
       <c r="V9">
-        <v>0.1017150963950042</v>
+        <v>0.1200980392156863</v>
       </c>
       <c r="W9">
-        <v>0.05633552227218322</v>
+        <v>0.1009638799850491</v>
       </c>
       <c r="X9">
-        <v>0.09598745376138404</v>
+        <v>0.08055180893824748</v>
       </c>
       <c r="Y9">
-        <v>-0.03965193148920082</v>
+        <v>0.02041207104680162</v>
       </c>
       <c r="Z9">
-        <v>0.1414413681727876</v>
+        <v>0.2187689732692276</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.08401525667871815</v>
+        <v>0.0706546071818086</v>
       </c>
       <c r="AC9">
-        <v>-0.08401525667871815</v>
+        <v>-0.0706546071818086</v>
       </c>
       <c r="AD9">
-        <v>2405.1</v>
+        <v>4018.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2405.1</v>
+        <v>4018.6</v>
       </c>
       <c r="AG9">
-        <v>2003.6</v>
+        <v>3288.5</v>
       </c>
       <c r="AH9">
-        <v>0.3786128077576979</v>
+        <v>0.3979678741904177</v>
       </c>
       <c r="AI9">
-        <v>0.2971790784742558</v>
+        <v>0.2874658425969641</v>
       </c>
       <c r="AJ9">
-        <v>0.3366885681157472</v>
+        <v>0.3510466816828037</v>
       </c>
       <c r="AK9">
-        <v>0.260491965260804</v>
+        <v>0.248201791792774</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1582,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
+          <t>CIMB Thai Bank Public Company Limited (SET:CIMBT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1591,13 +1588,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.031</v>
+        <v>0.0405</v>
       </c>
       <c r="E10">
-        <v>-0.0307</v>
-      </c>
-      <c r="F10">
-        <v>0.095</v>
+        <v>0.379</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1606,34 +1600,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.001276014038221358</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.001010345500295145</v>
       </c>
       <c r="K10">
-        <v>743.3</v>
+        <v>50.2</v>
       </c>
       <c r="L10">
-        <v>0.268319976896975</v>
+        <v>0.1711558131605864</v>
       </c>
       <c r="M10">
-        <v>202.2</v>
+        <v>11</v>
       </c>
       <c r="N10">
-        <v>0.02474181391023445</v>
+        <v>0.01741608613046232</v>
       </c>
       <c r="O10">
-        <v>0.2720301358805328</v>
+        <v>0.2191235059760956</v>
       </c>
       <c r="P10">
-        <v>202.2</v>
+        <v>11</v>
       </c>
       <c r="Q10">
-        <v>0.02474181391023445</v>
+        <v>0.01741608613046232</v>
       </c>
       <c r="R10">
-        <v>0.2720301358805328</v>
+        <v>0.2191235059760956</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1642,61 +1636,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1163.8</v>
+        <v>25</v>
       </c>
       <c r="V10">
-        <v>0.1424061475209241</v>
+        <v>0.03958201393286891</v>
       </c>
       <c r="W10">
-        <v>0.05132684698619636</v>
+        <v>0.04243807591512385</v>
       </c>
       <c r="X10">
-        <v>0.1100931073693448</v>
+        <v>0.21557140938856</v>
       </c>
       <c r="Y10">
-        <v>-0.05876626038314844</v>
+        <v>-0.1731333334734362</v>
       </c>
       <c r="Z10">
-        <v>0.1371834361722147</v>
+        <v>0.04600547087570016</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>4.648142048822299e-05</v>
       </c>
       <c r="AB10">
-        <v>0.08482627846663103</v>
+        <v>0.07108592219692016</v>
       </c>
       <c r="AC10">
-        <v>-0.08482627846663103</v>
+        <v>-0.07103944077643193</v>
       </c>
       <c r="AD10">
-        <v>8727.4</v>
+        <v>4318.7</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>2.128725412948379</v>
       </c>
       <c r="AF10">
-        <v>8727.4</v>
+        <v>4320.828725412948</v>
       </c>
       <c r="AG10">
-        <v>7563.599999999999</v>
+        <v>4295.828725412948</v>
       </c>
       <c r="AH10">
-        <v>0.5164203126664221</v>
+        <v>0.8724666148633293</v>
       </c>
       <c r="AI10">
-        <v>0.3915317804974338</v>
+        <v>0.771751756037127</v>
       </c>
       <c r="AJ10">
-        <v>0.4806558210472801</v>
+        <v>0.8718195563656644</v>
       </c>
       <c r="AK10">
-        <v>0.3580131208997188</v>
+        <v>0.7707279878596313</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>5398.374999999999</v>
+      </c>
+      <c r="AP10">
+        <v>5369.785906766185</v>
       </c>
     </row>
     <row r="11">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
+          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0138</v>
+        <v>0.0564</v>
       </c>
       <c r="E11">
-        <v>0.0179</v>
+        <v>0.0246</v>
       </c>
       <c r="F11">
-        <v>0.079</v>
+        <v>0.11</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1737,28 +1737,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1125.4</v>
+        <v>1103.4</v>
       </c>
       <c r="L11">
-        <v>0.3327321645034444</v>
+        <v>0.3153021860265752</v>
       </c>
       <c r="M11">
-        <v>227.5</v>
+        <v>261</v>
       </c>
       <c r="N11">
-        <v>0.02250336313998575</v>
+        <v>0.02986440871903427</v>
       </c>
       <c r="O11">
-        <v>0.2021503465434512</v>
+        <v>0.2365415986949429</v>
       </c>
       <c r="P11">
-        <v>227.5</v>
+        <v>261</v>
       </c>
       <c r="Q11">
-        <v>0.02250336313998575</v>
+        <v>0.02986440871903427</v>
       </c>
       <c r="R11">
-        <v>0.2021503465434512</v>
+        <v>0.2365415986949429</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1767,55 +1767,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1354.2</v>
+        <v>1094.2</v>
       </c>
       <c r="V11">
-        <v>0.1339518873150273</v>
+        <v>0.1252016705761199</v>
       </c>
       <c r="W11">
-        <v>0.08148341225364555</v>
+        <v>0.08165107743310443</v>
       </c>
       <c r="X11">
-        <v>0.1073264734706174</v>
+        <v>0.09014492078155514</v>
       </c>
       <c r="Y11">
-        <v>-0.02584306121697187</v>
+        <v>-0.008493843348450714</v>
       </c>
       <c r="Z11">
-        <v>0.1502610009107266</v>
+        <v>0.1660324900840719</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.08525504687432837</v>
+        <v>0.07209212760453068</v>
       </c>
       <c r="AC11">
-        <v>-0.08525504687432837</v>
+        <v>-0.07209212760453068</v>
       </c>
       <c r="AD11">
-        <v>9886.799999999999</v>
+        <v>9614.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>9886.799999999999</v>
+        <v>9614.6</v>
       </c>
       <c r="AG11">
-        <v>8532.599999999999</v>
+        <v>8520.4</v>
       </c>
       <c r="AH11">
-        <v>0.4944289972194995</v>
+        <v>0.5238393601429654</v>
       </c>
       <c r="AI11">
-        <v>0.4009278258542243</v>
+        <v>0.398787205096725</v>
       </c>
       <c r="AJ11">
-        <v>0.4577034899314458</v>
+        <v>0.4936529180354463</v>
       </c>
       <c r="AK11">
-        <v>0.3661180145544418</v>
+        <v>0.3702042979917794</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Krung Thai Bank Public Company Limited (SET:KTB)</t>
+          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0312</v>
+        <v>0.0153</v>
       </c>
       <c r="E12">
-        <v>0.04019999999999999</v>
+        <v>-0.00504</v>
       </c>
       <c r="F12">
-        <v>0.098</v>
+        <v>0.13</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1856,34 +1856,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.001490910416266843</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.001205774639768358</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>808.9</v>
+        <v>990.3</v>
       </c>
       <c r="L12">
-        <v>0.319281626208802</v>
+        <v>0.278283594672062</v>
       </c>
       <c r="M12">
-        <v>154.8</v>
+        <v>285.3</v>
       </c>
       <c r="N12">
-        <v>0.02163189446765696</v>
+        <v>0.03048891263692225</v>
       </c>
       <c r="O12">
-        <v>0.1913709976511312</v>
+        <v>0.288094516813087</v>
       </c>
       <c r="P12">
-        <v>154.8</v>
+        <v>285.3</v>
       </c>
       <c r="Q12">
-        <v>0.02163189446765696</v>
+        <v>0.03048891263692225</v>
       </c>
       <c r="R12">
-        <v>0.1913709976511312</v>
+        <v>0.288094516813087</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1892,67 +1892,61 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1468.2</v>
+        <v>1139.9</v>
       </c>
       <c r="V12">
-        <v>0.2051676192339403</v>
+        <v>0.121816724552498</v>
       </c>
       <c r="W12">
-        <v>0.07682299086367694</v>
+        <v>0.07472101287981106</v>
       </c>
       <c r="X12">
-        <v>0.1119478670956091</v>
+        <v>0.08760496010773849</v>
       </c>
       <c r="Y12">
-        <v>-0.03512487623193215</v>
+        <v>-0.01288394722792743</v>
       </c>
       <c r="Z12">
-        <v>0.1644259064944794</v>
+        <v>0.1633441813282903</v>
       </c>
       <c r="AA12">
-        <v>0.0001982605881719666</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.086723775552905</v>
+        <v>0.07230311209521073</v>
       </c>
       <c r="AC12">
-        <v>-0.08652551496473304</v>
+        <v>-0.07230311209521073</v>
       </c>
       <c r="AD12">
-        <v>8068.7</v>
+        <v>9206.6</v>
       </c>
       <c r="AE12">
-        <v>4.913892301939767</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>8073.61389230194</v>
+        <v>9206.6</v>
       </c>
       <c r="AG12">
-        <v>6605.41389230194</v>
+        <v>8066.700000000001</v>
       </c>
       <c r="AH12">
-        <v>0.5301224927398573</v>
+        <v>0.4959357038585227</v>
       </c>
       <c r="AI12">
-        <v>0.4467492452883501</v>
+        <v>0.3635250869663072</v>
       </c>
       <c r="AJ12">
-        <v>0.4799918049711773</v>
+        <v>0.4629595619884988</v>
       </c>
       <c r="AK12">
-        <v>0.3978274942068498</v>
+        <v>0.3335276606301166</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>1695.105042016807</v>
-      </c>
-      <c r="AP12">
-        <v>1387.69199418108</v>
       </c>
     </row>
     <row r="13">
@@ -1963,7 +1957,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CIMB Thai Bank Public Company Limited (SET:CIMBT)</t>
+          <t>Krung Thai Bank Public Company Limited (SET:KTB)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1972,7 +1966,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.136</v>
+        <v>0.0584</v>
+      </c>
+      <c r="E13">
+        <v>0.0731</v>
+      </c>
+      <c r="F13">
+        <v>0.09</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1981,34 +1981,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.001426592014536894</v>
+        <v>0.001341826317800198</v>
       </c>
       <c r="J13">
-        <v>0.001180237798810699</v>
+        <v>0.001071159879170562</v>
       </c>
       <c r="K13">
-        <v>93.90000000000001</v>
+        <v>1056.2</v>
       </c>
       <c r="L13">
-        <v>0.2898148148148149</v>
+        <v>0.3417901753931785</v>
       </c>
       <c r="M13">
-        <v>9.23</v>
+        <v>260.7</v>
       </c>
       <c r="N13">
-        <v>0.01103934936012439</v>
+        <v>0.03465280731603573</v>
       </c>
       <c r="O13">
-        <v>0.09829605963791267</v>
+        <v>0.2468282522249574</v>
       </c>
       <c r="P13">
-        <v>9.23</v>
+        <v>260.7</v>
       </c>
       <c r="Q13">
-        <v>0.01103934936012439</v>
+        <v>0.03465280731603573</v>
       </c>
       <c r="R13">
-        <v>0.09829605963791267</v>
+        <v>0.2468282522249574</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2017,55 +2017,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>22.7</v>
+        <v>1372.9</v>
       </c>
       <c r="V13">
-        <v>0.02714986245664394</v>
+        <v>0.1824888345384943</v>
       </c>
       <c r="W13">
-        <v>0.07504795396419438</v>
+        <v>0.1101527871929916</v>
       </c>
       <c r="X13">
-        <v>0.2691089308540316</v>
+        <v>0.08744360385919389</v>
       </c>
       <c r="Y13">
-        <v>-0.1940609768898372</v>
+        <v>0.02270918333379772</v>
       </c>
       <c r="Z13">
-        <v>0.05948546263498414</v>
+        <v>0.190791157010134</v>
       </c>
       <c r="AA13">
-        <v>7.020699148154979e-05</v>
+        <v>0.0002043678326897868</v>
       </c>
       <c r="AB13">
-        <v>0.08858594024423891</v>
+        <v>0.07281237544163126</v>
       </c>
       <c r="AC13">
-        <v>-0.08851573325275736</v>
+        <v>-0.07260800760894147</v>
       </c>
       <c r="AD13">
-        <v>5213</v>
+        <v>7339.3</v>
       </c>
       <c r="AE13">
-        <v>2.508920936450231</v>
+        <v>7.017441563669133</v>
       </c>
       <c r="AF13">
-        <v>5215.508920936451</v>
+        <v>7346.317441563669</v>
       </c>
       <c r="AG13">
-        <v>5192.808920936451</v>
+        <v>5973.41744156367</v>
       </c>
       <c r="AH13">
-        <v>0.8618383952228991</v>
+        <v>0.4940521755621369</v>
       </c>
       <c r="AI13">
-        <v>0.8151259141738515</v>
+        <v>0.3965384255355133</v>
       </c>
       <c r="AJ13">
-        <v>0.8613181902455856</v>
+        <v>0.4425862604038965</v>
       </c>
       <c r="AK13">
-        <v>0.8144676906256475</v>
+        <v>0.348238892319384</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2074,10 +2074,10 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>5407.676348547718</v>
+        <v>1322.396396396397</v>
       </c>
       <c r="AP13">
-        <v>5386.7312457847</v>
+        <v>1076.291430912373</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0352</v>
+        <v>0.0463</v>
       </c>
       <c r="E2">
-        <v>0.0147</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.07055</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0003230734402049593</v>
+        <v>0.0001068932046774008</v>
       </c>
       <c r="J2">
-        <v>0.0002622246895760832</v>
+        <v>9.009485011167705E-05</v>
       </c>
       <c r="K2">
-        <v>6251.9</v>
+        <v>5646.4</v>
       </c>
       <c r="L2">
-        <v>0.3189663528991607</v>
+        <v>0.3212434643590663</v>
       </c>
       <c r="M2">
-        <v>2349.1</v>
+        <v>1863.3</v>
       </c>
       <c r="N2">
-        <v>0.04412615523330077</v>
+        <v>0.04876242417263776</v>
       </c>
       <c r="O2">
-        <v>0.3757417745005519</v>
+        <v>0.3299978747520544</v>
       </c>
       <c r="P2">
-        <v>2349.1</v>
+        <v>1863.3</v>
       </c>
       <c r="Q2">
-        <v>0.04412615523330077</v>
+        <v>0.04876242417263776</v>
       </c>
       <c r="R2">
-        <v>0.3757417745005519</v>
+        <v>0.3299978747520544</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5791.58</v>
+        <v>5111.1</v>
       </c>
       <c r="V2">
-        <v>0.1087906679690435</v>
+        <v>0.1337571116775446</v>
       </c>
       <c r="W2">
-        <v>0.08958797787135661</v>
+        <v>0.1022417153996101</v>
       </c>
       <c r="X2">
-        <v>0.08760496010773849</v>
+        <v>0.0876299456955866</v>
       </c>
       <c r="Y2">
-        <v>0.001983017763618117</v>
+        <v>0.01461176970402353</v>
       </c>
       <c r="Z2">
-        <v>0.1754164423378456</v>
+        <v>0.211925824810795</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07024146141119464</v>
+        <v>0.0747522272519668</v>
       </c>
       <c r="AC2">
-        <v>-0.07024146141119464</v>
+        <v>-0.0747522272519668</v>
       </c>
       <c r="AD2">
-        <v>47958.8</v>
+        <v>30381.1</v>
       </c>
       <c r="AE2">
-        <v>14.53799517631348</v>
+        <v>4.005851046733644</v>
       </c>
       <c r="AF2">
-        <v>47973.33799517631</v>
+        <v>30385.10585104673</v>
       </c>
       <c r="AG2">
-        <v>42181.75799517631</v>
+        <v>25274.00585104674</v>
       </c>
       <c r="AH2">
-        <v>0.4740011044975192</v>
+        <v>0.4429515511534269</v>
       </c>
       <c r="AI2">
-        <v>0.3812808105796283</v>
+        <v>0.3048708336107604</v>
       </c>
       <c r="AJ2">
-        <v>0.4420745035458572</v>
+        <v>0.3981048285083716</v>
       </c>
       <c r="AK2">
-        <v>0.3514269162442886</v>
+        <v>0.2672959088851062</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>5190.346320346321</v>
+        <v>11336.23134328358</v>
       </c>
       <c r="AP2">
-        <v>4565.12532415328</v>
+        <v>9430.599198151765</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TISCO Financial Group Public Company Limited (SET:TISCO)</t>
+          <t>TMBThanachart Bank Public Company Limited (SET:TTB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0136</v>
+        <v>0.107</v>
       </c>
       <c r="E3">
-        <v>0.0147</v>
+        <v>0.233</v>
       </c>
       <c r="F3">
-        <v>0.0832</v>
+        <v>0.104</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>200.4</v>
+        <v>642.8</v>
       </c>
       <c r="L3">
-        <v>0.3995215311004784</v>
+        <v>0.4508030016130163</v>
       </c>
       <c r="M3">
-        <v>213.5</v>
+        <v>315.6</v>
       </c>
       <c r="N3">
-        <v>0.09137598972822598</v>
+        <v>0.05979197847791903</v>
       </c>
       <c r="O3">
-        <v>1.065369261477046</v>
+        <v>0.4909769757311762</v>
       </c>
       <c r="P3">
-        <v>213.5</v>
+        <v>315.6</v>
       </c>
       <c r="Q3">
-        <v>0.09137598972822598</v>
+        <v>0.05979197847791903</v>
       </c>
       <c r="R3">
-        <v>1.065369261477046</v>
+        <v>0.4909769757311762</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>21.8</v>
+        <v>385.4</v>
       </c>
       <c r="V3">
-        <v>0.009330194735715815</v>
+        <v>0.07301593316029782</v>
       </c>
       <c r="W3">
-        <v>0.1843945528156055</v>
+        <v>0.1050859095293368</v>
       </c>
       <c r="X3">
-        <v>0.07125336447664697</v>
+        <v>0.07858466131020729</v>
       </c>
       <c r="Y3">
-        <v>0.1131411883389585</v>
+        <v>0.02650124821912947</v>
       </c>
       <c r="Z3">
-        <v>0.3131672597864769</v>
+        <v>0.1851770083893925</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06719656201234664</v>
+        <v>0.07379804801132023</v>
       </c>
       <c r="AC3">
-        <v>-0.06719656201234664</v>
+        <v>-0.07379804801132023</v>
       </c>
       <c r="AD3">
-        <v>550.1</v>
+        <v>1900.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>550.1</v>
+        <v>1900.6</v>
       </c>
       <c r="AG3">
-        <v>528.3000000000001</v>
+        <v>1515.2</v>
       </c>
       <c r="AH3">
-        <v>0.1905702210212707</v>
+        <v>0.2647480811823538</v>
       </c>
       <c r="AI3">
-        <v>0.3319254208652628</v>
+        <v>0.2081777057296516</v>
       </c>
       <c r="AJ3">
-        <v>0.1844107791119799</v>
+        <v>0.2230367262824759</v>
       </c>
       <c r="AK3">
-        <v>0.3230204830327117</v>
+        <v>0.1732785929119541</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thanachart Capital Public Company Limited (SET:TCAP)</t>
+          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.216</v>
+        <v>0.0289</v>
       </c>
       <c r="E4">
-        <v>-0.0421</v>
+        <v>-0.00793</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.005947584898426812</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.005360689127052306</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>171.1</v>
+        <v>963.4</v>
       </c>
       <c r="L4">
-        <v>0.5617202889034799</v>
+        <v>0.285426480609131</v>
       </c>
       <c r="M4">
-        <v>88.8</v>
+        <v>195.1</v>
       </c>
       <c r="N4">
-        <v>0.05847876193612117</v>
+        <v>0.03715765817239934</v>
       </c>
       <c r="O4">
-        <v>0.5189947399181765</v>
+        <v>0.2025119368901806</v>
       </c>
       <c r="P4">
-        <v>88.8</v>
+        <v>195.1</v>
       </c>
       <c r="Q4">
-        <v>0.05847876193612117</v>
+        <v>0.03715765817239934</v>
       </c>
       <c r="R4">
-        <v>0.5189947399181765</v>
+        <v>0.2025119368901806</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,67 +892,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.18</v>
+        <v>767.9</v>
       </c>
       <c r="V4">
-        <v>0.000118538030951597</v>
+        <v>0.1462499523863939</v>
       </c>
       <c r="W4">
-        <v>0.09650310208685843</v>
+        <v>0.09748249483951917</v>
       </c>
       <c r="X4">
-        <v>0.09269070434888894</v>
+        <v>0.08902314271867584</v>
       </c>
       <c r="Y4">
-        <v>0.003812397737969486</v>
+        <v>0.008459352120843325</v>
       </c>
       <c r="Z4">
-        <v>0.08723884625562078</v>
+        <v>0.2562617205590944</v>
       </c>
       <c r="AA4">
-        <v>0.0004676603345790941</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06924021084811624</v>
+        <v>0.0744655310940994</v>
       </c>
       <c r="AC4">
-        <v>-0.06877255051353715</v>
+        <v>-0.0744655310940994</v>
       </c>
       <c r="AD4">
-        <v>1842.1</v>
+        <v>4582.3</v>
       </c>
       <c r="AE4">
-        <v>5.391828199695965</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1847.491828199696</v>
+        <v>4582.3</v>
       </c>
       <c r="AG4">
-        <v>1847.311828199696</v>
+        <v>3814.4</v>
       </c>
       <c r="AH4">
-        <v>0.548869968346842</v>
+        <v>0.4660171465183211</v>
       </c>
       <c r="AI4">
-        <v>0.4721430325730317</v>
+        <v>0.2759540628594485</v>
       </c>
       <c r="AJ4">
-        <v>0.5488458423974893</v>
+        <v>0.4207832322118036</v>
       </c>
       <c r="AK4">
-        <v>0.472118749714998</v>
+        <v>0.240847613876015</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>637.4048442906574</v>
-      </c>
-      <c r="AP4">
-        <v>639.2082450517978</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LH Financial Group Public Company Limited (SET:LHFG)</t>
+          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,10 +966,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00305</v>
+        <v>0.0669</v>
       </c>
       <c r="E5">
-        <v>-0.0751</v>
+        <v>0.0399</v>
+      </c>
+      <c r="F5">
+        <v>0.0738</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,28 +987,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>57.1</v>
+        <v>1350.4</v>
       </c>
       <c r="L5">
-        <v>0.3281609195402299</v>
+        <v>0.3149033416505375</v>
       </c>
       <c r="M5">
-        <v>5.8</v>
+        <v>413.1</v>
       </c>
       <c r="N5">
-        <v>0.009359367435856058</v>
+        <v>0.04919204067780464</v>
       </c>
       <c r="O5">
-        <v>0.1015761821366025</v>
+        <v>0.3059093601895734</v>
       </c>
       <c r="P5">
-        <v>5.8</v>
+        <v>413.1</v>
       </c>
       <c r="Q5">
-        <v>0.009359367435856058</v>
+        <v>0.04919204067780464</v>
       </c>
       <c r="R5">
-        <v>0.1015761821366025</v>
+        <v>0.3059093601895734</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1020,55 +1017,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>16</v>
+        <v>1294</v>
       </c>
       <c r="V5">
-        <v>0.0258189446506374</v>
+        <v>0.1540898103052026</v>
       </c>
       <c r="W5">
-        <v>0.06011159069375724</v>
+        <v>0.09348692955250333</v>
       </c>
       <c r="X5">
-        <v>0.08849668335293355</v>
+        <v>0.0922435846115796</v>
       </c>
       <c r="Y5">
-        <v>-0.02838509265917631</v>
+        <v>0.001243344940923735</v>
       </c>
       <c r="Z5">
-        <v>0.1059618780829426</v>
+        <v>0.186730357236166</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06899624535735799</v>
+        <v>0.0747522272519668</v>
       </c>
       <c r="AC5">
-        <v>-0.06899624535735799</v>
+        <v>-0.0747522272519668</v>
       </c>
       <c r="AD5">
-        <v>635</v>
+        <v>8657</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>635</v>
+        <v>8657</v>
       </c>
       <c r="AG5">
-        <v>619</v>
+        <v>7363</v>
       </c>
       <c r="AH5">
-        <v>0.5060970749980075</v>
+        <v>0.5076020100031077</v>
       </c>
       <c r="AI5">
-        <v>0.3964290173554751</v>
+        <v>0.3370672771801131</v>
       </c>
       <c r="AJ5">
-        <v>0.4997174457092112</v>
+        <v>0.467174681327606</v>
       </c>
       <c r="AK5">
-        <v>0.39033926094085</v>
+        <v>0.3018946833242447</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SCB X Public Company Limited (SET:SCB)</t>
+          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,13 +1091,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0156</v>
+        <v>0.0425</v>
       </c>
       <c r="E6">
-        <v>-0.0122</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="F6">
-        <v>-0.053</v>
+        <v>0.053</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,28 +1112,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1085</v>
+        <v>1468.6</v>
       </c>
       <c r="L6">
-        <v>0.316160615420479</v>
+        <v>0.3133213859020311</v>
       </c>
       <c r="M6">
-        <v>846.4</v>
+        <v>564.4</v>
       </c>
       <c r="N6">
-        <v>0.08106115021788057</v>
+        <v>0.05257960537347915</v>
       </c>
       <c r="O6">
-        <v>0.7800921658986175</v>
+        <v>0.3843115892686913</v>
       </c>
       <c r="P6">
-        <v>846.4</v>
+        <v>564.4</v>
       </c>
       <c r="Q6">
-        <v>0.08106115021788057</v>
+        <v>0.05257960537347915</v>
       </c>
       <c r="R6">
-        <v>0.7800921658986175</v>
+        <v>0.3843115892686913</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1145,55 +1142,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>993.9</v>
+        <v>1030.2</v>
       </c>
       <c r="V6">
-        <v>0.09518747306421491</v>
+        <v>0.09597361703713364</v>
       </c>
       <c r="W6">
-        <v>0.08958797787135661</v>
+        <v>0.1022417153996101</v>
       </c>
       <c r="X6">
-        <v>0.07700508658276684</v>
+        <v>0.0876299456955866</v>
       </c>
       <c r="Y6">
-        <v>0.01258289128858978</v>
+        <v>0.01461176970402353</v>
       </c>
       <c r="Z6">
-        <v>0.2205399430624193</v>
+        <v>0.2089636079123701</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06955473590073123</v>
+        <v>0.07482518834580291</v>
       </c>
       <c r="AC6">
-        <v>-0.06955473590073123</v>
+        <v>-0.07482518834580291</v>
       </c>
       <c r="AD6">
-        <v>5207.2</v>
+        <v>8633.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>5207.2</v>
+        <v>8633.5</v>
       </c>
       <c r="AG6">
-        <v>4213.3</v>
+        <v>7603.3</v>
       </c>
       <c r="AH6">
-        <v>0.3327560755845533</v>
+        <v>0.4457679538613258</v>
       </c>
       <c r="AI6">
-        <v>0.2874650826423469</v>
+        <v>0.3109288790930176</v>
       </c>
       <c r="AJ6">
-        <v>0.2875030706662663</v>
+        <v>0.4146312201772325</v>
       </c>
       <c r="AK6">
-        <v>0.2460996594685841</v>
+        <v>0.2843779687768827</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1210,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TMBThanachart Bank Public Company Limited (SET:TTB)</t>
+          <t>Krung Thai Bank Public Company Limited (SET:KTB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,13 +1216,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>0.0463</v>
       </c>
       <c r="E7">
-        <v>0.07490000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="F7">
-        <v>0.115</v>
+        <v>0.0673</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,34 +1231,34 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.0004944288922771767</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.0003978621429015742</v>
       </c>
       <c r="K7">
-        <v>477.1</v>
+        <v>1221.2</v>
       </c>
       <c r="L7">
-        <v>0.3304016620498615</v>
+        <v>0.3213684210526316</v>
       </c>
       <c r="M7">
-        <v>140.3</v>
+        <v>375.1</v>
       </c>
       <c r="N7">
-        <v>0.02957419898819562</v>
+        <v>0.04386621447783885</v>
       </c>
       <c r="O7">
-        <v>0.2940683294906728</v>
+        <v>0.3071568948575172</v>
       </c>
       <c r="P7">
-        <v>140.3</v>
+        <v>375.1</v>
       </c>
       <c r="Q7">
-        <v>0.02957419898819562</v>
+        <v>0.04386621447783885</v>
       </c>
       <c r="R7">
-        <v>0.2940683294906728</v>
+        <v>0.3071568948575172</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,55 +1267,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>371.2</v>
+        <v>1633.6</v>
       </c>
       <c r="V7">
-        <v>0.07824620573355817</v>
+        <v>0.1910419833937551</v>
       </c>
       <c r="W7">
-        <v>0.08387834036568215</v>
+        <v>0.1141372413406359</v>
       </c>
       <c r="X7">
-        <v>0.07511071374149716</v>
+        <v>0.08699688799193377</v>
       </c>
       <c r="Y7">
-        <v>0.008767626624184982</v>
+        <v>0.02714035334870217</v>
       </c>
       <c r="Z7">
-        <v>0.1877372718290083</v>
+        <v>0.227946466530073</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>9.06912696404968E-05</v>
       </c>
       <c r="AB7">
-        <v>0.07006818447553556</v>
+        <v>0.07544499135137808</v>
       </c>
       <c r="AC7">
-        <v>-0.07006818447553556</v>
+        <v>-0.07535430008173759</v>
       </c>
       <c r="AD7">
-        <v>1954.5</v>
+        <v>6607.7</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>4.005851046733644</v>
       </c>
       <c r="AF7">
-        <v>1954.5</v>
+        <v>6611.705851046733</v>
       </c>
       <c r="AG7">
-        <v>1583.3</v>
+        <v>4978.105851046734</v>
       </c>
       <c r="AH7">
-        <v>0.2917817421810853</v>
+        <v>0.4360505252820891</v>
       </c>
       <c r="AI7">
-        <v>0.2421512996506182</v>
+        <v>0.322830802237682</v>
       </c>
       <c r="AJ7">
-        <v>0.2502331168112781</v>
+        <v>0.367955274048032</v>
       </c>
       <c r="AK7">
-        <v>0.2056180358951716</v>
+        <v>0.2641352540260956</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1326,758 +1323,11 @@
       <c r="AM7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kiatnakin Phatra Bank Public Company Limited (SET:KKP)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0725</v>
-      </c>
-      <c r="E8">
-        <v>0.00942</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>169.7</v>
-      </c>
-      <c r="L8">
-        <v>0.2666142969363708</v>
-      </c>
-      <c r="M8">
-        <v>63.7</v>
-      </c>
-      <c r="N8">
-        <v>0.05117287917737789</v>
-      </c>
-      <c r="O8">
-        <v>0.3753682969946965</v>
-      </c>
-      <c r="P8">
-        <v>63.7</v>
-      </c>
-      <c r="Q8">
-        <v>0.05117287917737789</v>
-      </c>
-      <c r="R8">
-        <v>0.3753682969946965</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>26.4</v>
-      </c>
-      <c r="V8">
-        <v>0.02120822622107969</v>
-      </c>
-      <c r="W8">
-        <v>0.1195744081172491</v>
-      </c>
-      <c r="X8">
-        <v>0.1235387367767436</v>
-      </c>
-      <c r="Y8">
-        <v>-0.003964328659494476</v>
-      </c>
-      <c r="Z8">
-        <v>0.1542768499890928</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.07024146141119464</v>
-      </c>
-      <c r="AC8">
-        <v>-0.07024146141119464</v>
-      </c>
-      <c r="AD8">
-        <v>3272.1</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>3272.1</v>
-      </c>
-      <c r="AG8">
-        <v>3245.7</v>
-      </c>
-      <c r="AH8">
-        <v>0.7244127609643782</v>
-      </c>
-      <c r="AI8">
-        <v>0.6645072195934282</v>
-      </c>
-      <c r="AJ8">
-        <v>0.7227925620754927</v>
-      </c>
-      <c r="AK8">
-        <v>0.6626988178124426</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.0352</v>
-      </c>
-      <c r="E9">
-        <v>0.05980000000000001</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>891.4</v>
-      </c>
-      <c r="L9">
-        <v>0.3343084308430843</v>
-      </c>
-      <c r="M9">
-        <v>172.6</v>
-      </c>
-      <c r="N9">
-        <v>0.02839189367021977</v>
-      </c>
-      <c r="O9">
-        <v>0.1936280008974647</v>
-      </c>
-      <c r="P9">
-        <v>172.6</v>
-      </c>
-      <c r="Q9">
-        <v>0.02839189367021977</v>
-      </c>
-      <c r="R9">
-        <v>0.1936280008974647</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>730.1</v>
-      </c>
-      <c r="V9">
-        <v>0.1200980392156863</v>
-      </c>
-      <c r="W9">
-        <v>0.1009638799850491</v>
-      </c>
-      <c r="X9">
-        <v>0.08055180893824748</v>
-      </c>
-      <c r="Y9">
-        <v>0.02041207104680162</v>
-      </c>
-      <c r="Z9">
-        <v>0.2187689732692276</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.0706546071818086</v>
-      </c>
-      <c r="AC9">
-        <v>-0.0706546071818086</v>
-      </c>
-      <c r="AD9">
-        <v>4018.6</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>4018.6</v>
-      </c>
-      <c r="AG9">
-        <v>3288.5</v>
-      </c>
-      <c r="AH9">
-        <v>0.3979678741904177</v>
-      </c>
-      <c r="AI9">
-        <v>0.2874658425969641</v>
-      </c>
-      <c r="AJ9">
-        <v>0.3510466816828037</v>
-      </c>
-      <c r="AK9">
-        <v>0.248201791792774</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CIMB Thai Bank Public Company Limited (SET:CIMBT)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.0405</v>
-      </c>
-      <c r="E10">
-        <v>0.379</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0.001276014038221358</v>
-      </c>
-      <c r="J10">
-        <v>0.001010345500295145</v>
-      </c>
-      <c r="K10">
-        <v>50.2</v>
-      </c>
-      <c r="L10">
-        <v>0.1711558131605864</v>
-      </c>
-      <c r="M10">
-        <v>11</v>
-      </c>
-      <c r="N10">
-        <v>0.01741608613046232</v>
-      </c>
-      <c r="O10">
-        <v>0.2191235059760956</v>
-      </c>
-      <c r="P10">
-        <v>11</v>
-      </c>
-      <c r="Q10">
-        <v>0.01741608613046232</v>
-      </c>
-      <c r="R10">
-        <v>0.2191235059760956</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>25</v>
-      </c>
-      <c r="V10">
-        <v>0.03958201393286891</v>
-      </c>
-      <c r="W10">
-        <v>0.04243807591512385</v>
-      </c>
-      <c r="X10">
-        <v>0.21557140938856</v>
-      </c>
-      <c r="Y10">
-        <v>-0.1731333334734362</v>
-      </c>
-      <c r="Z10">
-        <v>0.04600547087570016</v>
-      </c>
-      <c r="AA10">
-        <v>4.648142048822299e-05</v>
-      </c>
-      <c r="AB10">
-        <v>0.07108592219692016</v>
-      </c>
-      <c r="AC10">
-        <v>-0.07103944077643193</v>
-      </c>
-      <c r="AD10">
-        <v>4318.7</v>
-      </c>
-      <c r="AE10">
-        <v>2.128725412948379</v>
-      </c>
-      <c r="AF10">
-        <v>4320.828725412948</v>
-      </c>
-      <c r="AG10">
-        <v>4295.828725412948</v>
-      </c>
-      <c r="AH10">
-        <v>0.8724666148633293</v>
-      </c>
-      <c r="AI10">
-        <v>0.771751756037127</v>
-      </c>
-      <c r="AJ10">
-        <v>0.8718195563656644</v>
-      </c>
-      <c r="AK10">
-        <v>0.7707279878596313</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>5398.374999999999</v>
-      </c>
-      <c r="AP10">
-        <v>5369.785906766185</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.0564</v>
-      </c>
-      <c r="E11">
-        <v>0.0246</v>
-      </c>
-      <c r="F11">
-        <v>0.11</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>1103.4</v>
-      </c>
-      <c r="L11">
-        <v>0.3153021860265752</v>
-      </c>
-      <c r="M11">
-        <v>261</v>
-      </c>
-      <c r="N11">
-        <v>0.02986440871903427</v>
-      </c>
-      <c r="O11">
-        <v>0.2365415986949429</v>
-      </c>
-      <c r="P11">
-        <v>261</v>
-      </c>
-      <c r="Q11">
-        <v>0.02986440871903427</v>
-      </c>
-      <c r="R11">
-        <v>0.2365415986949429</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>1094.2</v>
-      </c>
-      <c r="V11">
-        <v>0.1252016705761199</v>
-      </c>
-      <c r="W11">
-        <v>0.08165107743310443</v>
-      </c>
-      <c r="X11">
-        <v>0.09014492078155514</v>
-      </c>
-      <c r="Y11">
-        <v>-0.008493843348450714</v>
-      </c>
-      <c r="Z11">
-        <v>0.1660324900840719</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.07209212760453068</v>
-      </c>
-      <c r="AC11">
-        <v>-0.07209212760453068</v>
-      </c>
-      <c r="AD11">
-        <v>9614.6</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>9614.6</v>
-      </c>
-      <c r="AG11">
-        <v>8520.4</v>
-      </c>
-      <c r="AH11">
-        <v>0.5238393601429654</v>
-      </c>
-      <c r="AI11">
-        <v>0.398787205096725</v>
-      </c>
-      <c r="AJ11">
-        <v>0.4936529180354463</v>
-      </c>
-      <c r="AK11">
-        <v>0.3702042979917794</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.0153</v>
-      </c>
-      <c r="E12">
-        <v>-0.00504</v>
-      </c>
-      <c r="F12">
-        <v>0.13</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>990.3</v>
-      </c>
-      <c r="L12">
-        <v>0.278283594672062</v>
-      </c>
-      <c r="M12">
-        <v>285.3</v>
-      </c>
-      <c r="N12">
-        <v>0.03048891263692225</v>
-      </c>
-      <c r="O12">
-        <v>0.288094516813087</v>
-      </c>
-      <c r="P12">
-        <v>285.3</v>
-      </c>
-      <c r="Q12">
-        <v>0.03048891263692225</v>
-      </c>
-      <c r="R12">
-        <v>0.288094516813087</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>1139.9</v>
-      </c>
-      <c r="V12">
-        <v>0.121816724552498</v>
-      </c>
-      <c r="W12">
-        <v>0.07472101287981106</v>
-      </c>
-      <c r="X12">
-        <v>0.08760496010773849</v>
-      </c>
-      <c r="Y12">
-        <v>-0.01288394722792743</v>
-      </c>
-      <c r="Z12">
-        <v>0.1633441813282903</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.07230311209521073</v>
-      </c>
-      <c r="AC12">
-        <v>-0.07230311209521073</v>
-      </c>
-      <c r="AD12">
-        <v>9206.6</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>9206.6</v>
-      </c>
-      <c r="AG12">
-        <v>8066.700000000001</v>
-      </c>
-      <c r="AH12">
-        <v>0.4959357038585227</v>
-      </c>
-      <c r="AI12">
-        <v>0.3635250869663072</v>
-      </c>
-      <c r="AJ12">
-        <v>0.4629595619884988</v>
-      </c>
-      <c r="AK12">
-        <v>0.3335276606301166</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Krung Thai Bank Public Company Limited (SET:KTB)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0584</v>
-      </c>
-      <c r="E13">
-        <v>0.0731</v>
-      </c>
-      <c r="F13">
-        <v>0.09</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0.001341826317800198</v>
-      </c>
-      <c r="J13">
-        <v>0.001071159879170562</v>
-      </c>
-      <c r="K13">
-        <v>1056.2</v>
-      </c>
-      <c r="L13">
-        <v>0.3417901753931785</v>
-      </c>
-      <c r="M13">
-        <v>260.7</v>
-      </c>
-      <c r="N13">
-        <v>0.03465280731603573</v>
-      </c>
-      <c r="O13">
-        <v>0.2468282522249574</v>
-      </c>
-      <c r="P13">
-        <v>260.7</v>
-      </c>
-      <c r="Q13">
-        <v>0.03465280731603573</v>
-      </c>
-      <c r="R13">
-        <v>0.2468282522249574</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>1372.9</v>
-      </c>
-      <c r="V13">
-        <v>0.1824888345384943</v>
-      </c>
-      <c r="W13">
-        <v>0.1101527871929916</v>
-      </c>
-      <c r="X13">
-        <v>0.08744360385919389</v>
-      </c>
-      <c r="Y13">
-        <v>0.02270918333379772</v>
-      </c>
-      <c r="Z13">
-        <v>0.190791157010134</v>
-      </c>
-      <c r="AA13">
-        <v>0.0002043678326897868</v>
-      </c>
-      <c r="AB13">
-        <v>0.07281237544163126</v>
-      </c>
-      <c r="AC13">
-        <v>-0.07260800760894147</v>
-      </c>
-      <c r="AD13">
-        <v>7339.3</v>
-      </c>
-      <c r="AE13">
-        <v>7.017441563669133</v>
-      </c>
-      <c r="AF13">
-        <v>7346.317441563669</v>
-      </c>
-      <c r="AG13">
-        <v>5973.41744156367</v>
-      </c>
-      <c r="AH13">
-        <v>0.4940521755621369</v>
-      </c>
-      <c r="AI13">
-        <v>0.3965384255355133</v>
-      </c>
-      <c r="AJ13">
-        <v>0.4425862604038965</v>
-      </c>
-      <c r="AK13">
-        <v>0.348238892319384</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1322.396396396397</v>
-      </c>
-      <c r="AP13">
-        <v>1076.291430912373</v>
+      <c r="AN7">
+        <v>2465.559701492537</v>
+      </c>
+      <c r="AP7">
+        <v>1857.502183226393</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0463</v>
+        <v>0.0357</v>
       </c>
       <c r="E2">
-        <v>0.05139999999999999</v>
+        <v>0.00573</v>
       </c>
       <c r="F2">
-        <v>0.07055</v>
+        <v>0.06015</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0001068932046774008</v>
+        <v>0.0001655509485342296</v>
       </c>
       <c r="J2">
-        <v>9.009485011167705E-05</v>
+        <v>0.0001371082505249521</v>
       </c>
       <c r="K2">
-        <v>5646.4</v>
+        <v>7747.7</v>
       </c>
       <c r="L2">
-        <v>0.3212434643590663</v>
+        <v>0.3230052154771682</v>
       </c>
       <c r="M2">
-        <v>1863.3</v>
+        <v>3269.28</v>
       </c>
       <c r="N2">
-        <v>0.04876242417263776</v>
+        <v>0.05790353661301292</v>
       </c>
       <c r="O2">
-        <v>0.3299978747520544</v>
+        <v>0.4219678098016185</v>
       </c>
       <c r="P2">
-        <v>1863.3</v>
+        <v>3252.88</v>
       </c>
       <c r="Q2">
-        <v>0.04876242417263776</v>
+        <v>0.05761306959873044</v>
       </c>
       <c r="R2">
-        <v>0.3299978747520544</v>
+        <v>0.4198510525704403</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.005016395047227524</v>
       </c>
       <c r="U2">
-        <v>5111.1</v>
+        <v>6385.4</v>
       </c>
       <c r="V2">
-        <v>0.1337571116775446</v>
+        <v>0.1130943946950805</v>
       </c>
       <c r="W2">
-        <v>0.1022417153996101</v>
+        <v>0.1035172642658179</v>
       </c>
       <c r="X2">
-        <v>0.0876299456955866</v>
+        <v>0.09062123348882226</v>
       </c>
       <c r="Y2">
-        <v>0.01461176970402353</v>
+        <v>0.01289603077699569</v>
       </c>
       <c r="Z2">
-        <v>0.211925824810795</v>
+        <v>0.2025281006264186</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0747522272519668</v>
+        <v>0.07398157760118748</v>
       </c>
       <c r="AC2">
-        <v>-0.0747522272519668</v>
+        <v>-0.07395683337262687</v>
       </c>
       <c r="AD2">
-        <v>30381.1</v>
+        <v>46678.6</v>
       </c>
       <c r="AE2">
-        <v>4.005851046733644</v>
+        <v>10.73022641586705</v>
       </c>
       <c r="AF2">
-        <v>30385.10585104673</v>
+        <v>46689.33022641587</v>
       </c>
       <c r="AG2">
-        <v>25274.00585104674</v>
+        <v>40303.93022641587</v>
       </c>
       <c r="AH2">
-        <v>0.4429515511534269</v>
+        <v>0.4526347191606272</v>
       </c>
       <c r="AI2">
-        <v>0.3048708336107604</v>
+        <v>0.3336743746686467</v>
       </c>
       <c r="AJ2">
-        <v>0.3981048285083716</v>
+        <v>0.4165146756686071</v>
       </c>
       <c r="AK2">
-        <v>0.2672959088851062</v>
+        <v>0.301812956353645</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>11336.23134328358</v>
+        <v>7630.962890305706</v>
       </c>
       <c r="AP2">
-        <v>9430.599198151765</v>
+        <v>6588.839337324811</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TMBThanachart Bank Public Company Limited (SET:TTB)</t>
+          <t>TISCO Financial Group Public Company Limited (SET:TISCO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.107</v>
+        <v>0.00032</v>
       </c>
       <c r="E3">
-        <v>0.233</v>
+        <v>-0.00428</v>
       </c>
       <c r="F3">
-        <v>0.104</v>
+        <v>-0.0492</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>642.8</v>
+        <v>215.8</v>
       </c>
       <c r="L3">
-        <v>0.4508030016130163</v>
+        <v>0.3884788478847885</v>
       </c>
       <c r="M3">
-        <v>315.6</v>
+        <v>191.8</v>
       </c>
       <c r="N3">
-        <v>0.05979197847791903</v>
+        <v>0.08347477912695306</v>
       </c>
       <c r="O3">
-        <v>0.4909769757311762</v>
+        <v>0.8887859128822985</v>
       </c>
       <c r="P3">
-        <v>315.6</v>
+        <v>191.8</v>
       </c>
       <c r="Q3">
-        <v>0.05979197847791903</v>
+        <v>0.08347477912695306</v>
       </c>
       <c r="R3">
-        <v>0.4909769757311762</v>
+        <v>0.8887859128822985</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>385.4</v>
+        <v>27.7</v>
       </c>
       <c r="V3">
-        <v>0.07301593316029782</v>
+        <v>0.01205553379466423</v>
       </c>
       <c r="W3">
-        <v>0.1050859095293368</v>
+        <v>0.194923674464818</v>
       </c>
       <c r="X3">
-        <v>0.07858466131020729</v>
+        <v>0.07618590853848749</v>
       </c>
       <c r="Y3">
-        <v>0.02650124821912947</v>
+        <v>0.1187377659263305</v>
       </c>
       <c r="Z3">
-        <v>0.1851770083893925</v>
+        <v>0.3396722514369573</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07379804801132023</v>
+        <v>0.0718737745984933</v>
       </c>
       <c r="AC3">
-        <v>-0.07379804801132023</v>
+        <v>-0.0718737745984933</v>
       </c>
       <c r="AD3">
-        <v>1900.6</v>
+        <v>557.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1900.6</v>
+        <v>557.6</v>
       </c>
       <c r="AG3">
-        <v>1515.2</v>
+        <v>529.9</v>
       </c>
       <c r="AH3">
-        <v>0.2647480811823538</v>
+        <v>0.1952859594438413</v>
       </c>
       <c r="AI3">
-        <v>0.2081777057296516</v>
+        <v>0.3030599489102669</v>
       </c>
       <c r="AJ3">
-        <v>0.2230367262824759</v>
+        <v>0.1874027443768567</v>
       </c>
       <c r="AK3">
-        <v>0.1732785929119541</v>
+        <v>0.2924070190928154</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
+          <t>SCB X Public Company Limited (SET:SCB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0289</v>
+        <v>-0.00063</v>
       </c>
       <c r="E4">
-        <v>-0.00793</v>
+        <v>0.00573</v>
+      </c>
+      <c r="F4">
+        <v>-0.008829999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,28 +865,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>963.4</v>
+        <v>1336.8</v>
       </c>
       <c r="L4">
-        <v>0.285426480609131</v>
+        <v>0.3352140224178139</v>
       </c>
       <c r="M4">
-        <v>195.1</v>
+        <v>1024.6</v>
       </c>
       <c r="N4">
-        <v>0.03715765817239934</v>
+        <v>0.08888850331401603</v>
       </c>
       <c r="O4">
-        <v>0.2025119368901806</v>
+        <v>0.7664572112507481</v>
       </c>
       <c r="P4">
-        <v>195.1</v>
+        <v>1024.6</v>
       </c>
       <c r="Q4">
-        <v>0.03715765817239934</v>
+        <v>0.08888850331401603</v>
       </c>
       <c r="R4">
-        <v>0.2025119368901806</v>
+        <v>0.7664572112507481</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,55 +895,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>767.9</v>
+        <v>1150.1</v>
       </c>
       <c r="V4">
-        <v>0.1462499523863939</v>
+        <v>0.0997761737863067</v>
       </c>
       <c r="W4">
-        <v>0.09748249483951917</v>
+        <v>0.1047928131320258</v>
       </c>
       <c r="X4">
-        <v>0.08902314271867584</v>
+        <v>0.08024778171450361</v>
       </c>
       <c r="Y4">
-        <v>0.008459352120843325</v>
+        <v>0.02454503141752215</v>
       </c>
       <c r="Z4">
-        <v>0.2562617205590944</v>
+        <v>0.2349984384115405</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0744655310940994</v>
+        <v>0.07223178618049308</v>
       </c>
       <c r="AC4">
-        <v>-0.0744655310940994</v>
+        <v>-0.07223178618049308</v>
       </c>
       <c r="AD4">
-        <v>4582.3</v>
+        <v>5097.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4582.3</v>
+        <v>5097.3</v>
       </c>
       <c r="AG4">
-        <v>3814.4</v>
+        <v>3947.2</v>
       </c>
       <c r="AH4">
-        <v>0.4660171465183211</v>
+        <v>0.3066211103157465</v>
       </c>
       <c r="AI4">
-        <v>0.2759540628594485</v>
+        <v>0.2542294264339152</v>
       </c>
       <c r="AJ4">
-        <v>0.4207832322118036</v>
+        <v>0.255085950626858</v>
       </c>
       <c r="AK4">
-        <v>0.240847613876015</v>
+        <v>0.2088476658606659</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
+          <t>Thanachart Capital Public Company Limited (SET:TCAP)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,14 +968,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.0669</v>
-      </c>
       <c r="E5">
-        <v>0.0399</v>
-      </c>
-      <c r="F5">
-        <v>0.0738</v>
+        <v>-0.0432</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,34 +978,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.005082436316552825</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.004748319137714965</v>
       </c>
       <c r="K5">
-        <v>1350.4</v>
+        <v>208.5</v>
       </c>
       <c r="L5">
-        <v>0.3149033416505375</v>
+        <v>0.6061046511627907</v>
       </c>
       <c r="M5">
-        <v>413.1</v>
+        <v>144.2</v>
       </c>
       <c r="N5">
-        <v>0.04919204067780464</v>
+        <v>0.09346642468239565</v>
       </c>
       <c r="O5">
-        <v>0.3059093601895734</v>
+        <v>0.6916067146282973</v>
       </c>
       <c r="P5">
-        <v>413.1</v>
+        <v>144.2</v>
       </c>
       <c r="Q5">
-        <v>0.04919204067780464</v>
+        <v>0.09346642468239565</v>
       </c>
       <c r="R5">
-        <v>0.3059093601895734</v>
+        <v>0.6916067146282973</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,61 +1014,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1294</v>
+        <v>0.2</v>
       </c>
       <c r="V5">
-        <v>0.1540898103052026</v>
+        <v>0.0001296344309048483</v>
       </c>
       <c r="W5">
-        <v>0.09348692955250333</v>
+        <v>0.1093799181617879</v>
       </c>
       <c r="X5">
-        <v>0.0922435846115796</v>
+        <v>0.09784625503275367</v>
       </c>
       <c r="Y5">
-        <v>0.001243344940923735</v>
+        <v>0.01153366312903419</v>
       </c>
       <c r="Z5">
-        <v>0.186730357236166</v>
+        <v>0.09166166101427507</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.000435238819188824</v>
       </c>
       <c r="AB5">
-        <v>0.0747522272519668</v>
+        <v>0.07306740685973312</v>
       </c>
       <c r="AC5">
-        <v>-0.0747522272519668</v>
+        <v>-0.0726321680405443</v>
       </c>
       <c r="AD5">
-        <v>8657</v>
+        <v>2011.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>4.808209535529141</v>
       </c>
       <c r="AF5">
-        <v>8657</v>
+        <v>2016.008209535529</v>
       </c>
       <c r="AG5">
-        <v>7363</v>
+        <v>2015.808209535529</v>
       </c>
       <c r="AH5">
-        <v>0.5076020100031077</v>
+        <v>0.5664840842318515</v>
       </c>
       <c r="AI5">
-        <v>0.3370672771801131</v>
+        <v>0.4557487211597627</v>
       </c>
       <c r="AJ5">
-        <v>0.467174681327606</v>
+        <v>0.5664597198798216</v>
       </c>
       <c r="AK5">
-        <v>0.3018946833242447</v>
+        <v>0.4557241128235103</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>742.140221402214</v>
+      </c>
+      <c r="AP5">
+        <v>743.8406677252875</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
+          <t>LH Financial Group Public Company Limited (SET:LHFG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,13 +1094,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0425</v>
+        <v>-0.00168</v>
       </c>
       <c r="E6">
-        <v>0.05139999999999999</v>
-      </c>
-      <c r="F6">
-        <v>0.053</v>
+        <v>-0.1</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,28 +1112,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1468.6</v>
+        <v>56.3</v>
       </c>
       <c r="L6">
-        <v>0.3133213859020311</v>
+        <v>0.279265873015873</v>
       </c>
       <c r="M6">
-        <v>564.4</v>
+        <v>19.7</v>
       </c>
       <c r="N6">
-        <v>0.05257960537347915</v>
+        <v>0.04092230992937267</v>
       </c>
       <c r="O6">
-        <v>0.3843115892686913</v>
+        <v>0.349911190053286</v>
       </c>
       <c r="P6">
-        <v>564.4</v>
+        <v>19.7</v>
       </c>
       <c r="Q6">
-        <v>0.05257960537347915</v>
+        <v>0.04092230992937267</v>
       </c>
       <c r="R6">
-        <v>0.3843115892686913</v>
+        <v>0.349911190053286</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1142,55 +1142,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1030.2</v>
+        <v>25.7</v>
       </c>
       <c r="V6">
-        <v>0.09597361703713364</v>
+        <v>0.05338595762359784</v>
       </c>
       <c r="W6">
-        <v>0.1022417153996101</v>
+        <v>0.05823334712453455</v>
       </c>
       <c r="X6">
-        <v>0.0876299456955866</v>
+        <v>0.1074640649720776</v>
       </c>
       <c r="Y6">
-        <v>0.01461176970402353</v>
+        <v>-0.04923071784754308</v>
       </c>
       <c r="Z6">
-        <v>0.2089636079123701</v>
+        <v>0.1271282633371169</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07482518834580291</v>
+        <v>0.07330439258789183</v>
       </c>
       <c r="AC6">
-        <v>-0.07482518834580291</v>
+        <v>-0.07330439258789183</v>
       </c>
       <c r="AD6">
-        <v>8633.5</v>
+        <v>856.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>8633.5</v>
+        <v>856.5</v>
       </c>
       <c r="AG6">
-        <v>7603.3</v>
+        <v>830.8</v>
       </c>
       <c r="AH6">
-        <v>0.4457679538613258</v>
+        <v>0.6401823753643769</v>
       </c>
       <c r="AI6">
-        <v>0.3109288790930176</v>
+        <v>0.4184785264083647</v>
       </c>
       <c r="AJ6">
-        <v>0.4146312201772325</v>
+        <v>0.6331351928059747</v>
       </c>
       <c r="AK6">
-        <v>0.2843779687768827</v>
+        <v>0.4110836219693221</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,127 +1207,984 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Kiatnakin Phatra Bank Public Company Limited (SET:KKP)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0469</v>
+      </c>
+      <c r="E7">
+        <v>-0.0582</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>131.4</v>
+      </c>
+      <c r="L7">
+        <v>0.1934059464233147</v>
+      </c>
+      <c r="M7">
+        <v>25.68</v>
+      </c>
+      <c r="N7">
+        <v>0.02008918094344051</v>
+      </c>
+      <c r="O7">
+        <v>0.1954337899543379</v>
+      </c>
+      <c r="P7">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="Q7">
+        <v>0.007259641711648283</v>
+      </c>
+      <c r="R7">
+        <v>0.07062404870624048</v>
+      </c>
+      <c r="S7">
+        <v>16.4</v>
+      </c>
+      <c r="T7">
+        <v>0.6386292834890965</v>
+      </c>
+      <c r="U7">
+        <v>28.6</v>
+      </c>
+      <c r="V7">
+        <v>0.02237346475788156</v>
+      </c>
+      <c r="W7">
+        <v>0.07993673196252586</v>
+      </c>
+      <c r="X7">
+        <v>0.1099271015916125</v>
+      </c>
+      <c r="Y7">
+        <v>-0.02999036962908662</v>
+      </c>
+      <c r="Z7">
+        <v>0.1413767271516564</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.07335266365304172</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07335266365304172</v>
+      </c>
+      <c r="AD7">
+        <v>2429</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>2429</v>
+      </c>
+      <c r="AG7">
+        <v>2400.4</v>
+      </c>
+      <c r="AH7">
+        <v>0.655193806813584</v>
+      </c>
+      <c r="AI7">
+        <v>0.5587504600662495</v>
+      </c>
+      <c r="AJ7">
+        <v>0.6525131160464295</v>
+      </c>
+      <c r="AK7">
+        <v>0.5558282776825823</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TMBThanachart Bank Public Company Limited (SET:TTB)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.107</v>
+      </c>
+      <c r="E8">
+        <v>0.233</v>
+      </c>
+      <c r="F8">
+        <v>0.104</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>642.8</v>
+      </c>
+      <c r="L8">
+        <v>0.4508030016130163</v>
+      </c>
+      <c r="M8">
+        <v>315.6</v>
+      </c>
+      <c r="N8">
+        <v>0.05979197847791903</v>
+      </c>
+      <c r="O8">
+        <v>0.4909769757311762</v>
+      </c>
+      <c r="P8">
+        <v>315.6</v>
+      </c>
+      <c r="Q8">
+        <v>0.05979197847791903</v>
+      </c>
+      <c r="R8">
+        <v>0.4909769757311762</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>385.4</v>
+      </c>
+      <c r="V8">
+        <v>0.07301593316029782</v>
+      </c>
+      <c r="W8">
+        <v>0.1050859095293368</v>
+      </c>
+      <c r="X8">
+        <v>0.07857579104732051</v>
+      </c>
+      <c r="Y8">
+        <v>0.02651011848201625</v>
+      </c>
+      <c r="Z8">
+        <v>0.1851770083893925</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.07379152613351231</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07379152613351231</v>
+      </c>
+      <c r="AD8">
+        <v>1900.6</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>1900.6</v>
+      </c>
+      <c r="AG8">
+        <v>1515.2</v>
+      </c>
+      <c r="AH8">
+        <v>0.2647480811823538</v>
+      </c>
+      <c r="AI8">
+        <v>0.2081777057296516</v>
+      </c>
+      <c r="AJ8">
+        <v>0.2230367262824759</v>
+      </c>
+      <c r="AK8">
+        <v>0.1732785929119541</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CIMB Thai Bank Public Company Limited (SET:CIMBT)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0174</v>
+      </c>
+      <c r="E9">
+        <v>0.301</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.000997003576795672</v>
+      </c>
+      <c r="J9">
+        <v>0.0007999556722372354</v>
+      </c>
+      <c r="K9">
+        <v>54.4</v>
+      </c>
+      <c r="L9">
+        <v>0.1577726218097448</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>28.5</v>
+      </c>
+      <c r="V9">
+        <v>0.0624315443592552</v>
+      </c>
+      <c r="W9">
+        <v>0.04256984114562955</v>
+      </c>
+      <c r="X9">
+        <v>0.2767661705469255</v>
+      </c>
+      <c r="Y9">
+        <v>-0.2341963294012959</v>
+      </c>
+      <c r="Z9">
+        <v>0.061863999267405</v>
+      </c>
+      <c r="AA9">
+        <v>4.948845712124079E-05</v>
+      </c>
+      <c r="AB9">
+        <v>0.07417162906886267</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07412214061174142</v>
+      </c>
+      <c r="AD9">
+        <v>4606.9</v>
+      </c>
+      <c r="AE9">
+        <v>1.916165833604262</v>
+      </c>
+      <c r="AF9">
+        <v>4608.816165833604</v>
+      </c>
+      <c r="AG9">
+        <v>4580.316165833604</v>
+      </c>
+      <c r="AH9">
+        <v>0.9098772939230985</v>
+      </c>
+      <c r="AI9">
+        <v>0.7509987168298834</v>
+      </c>
+      <c r="AJ9">
+        <v>0.9093673493393325</v>
+      </c>
+      <c r="AK9">
+        <v>0.7498369530636814</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>6336.863823933975</v>
+      </c>
+      <c r="AP9">
+        <v>6300.297339523527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bank of Ayudhya Public Company Limited (SET:BAY)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0289</v>
+      </c>
+      <c r="E10">
+        <v>-0.00793</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>963.4</v>
+      </c>
+      <c r="L10">
+        <v>0.285426480609131</v>
+      </c>
+      <c r="M10">
+        <v>195.1</v>
+      </c>
+      <c r="N10">
+        <v>0.03715765817239934</v>
+      </c>
+      <c r="O10">
+        <v>0.2025119368901806</v>
+      </c>
+      <c r="P10">
+        <v>195.1</v>
+      </c>
+      <c r="Q10">
+        <v>0.03715765817239934</v>
+      </c>
+      <c r="R10">
+        <v>0.2025119368901806</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>767.9</v>
+      </c>
+      <c r="V10">
+        <v>0.1462499523863939</v>
+      </c>
+      <c r="W10">
+        <v>0.09748249483951917</v>
+      </c>
+      <c r="X10">
+        <v>0.08901144820595602</v>
+      </c>
+      <c r="Y10">
+        <v>0.008471046633563142</v>
+      </c>
+      <c r="Z10">
+        <v>0.2562617205590944</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.07445928642482719</v>
+      </c>
+      <c r="AC10">
+        <v>-0.07445928642482719</v>
+      </c>
+      <c r="AD10">
+        <v>4582.3</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>4582.3</v>
+      </c>
+      <c r="AG10">
+        <v>3814.4</v>
+      </c>
+      <c r="AH10">
+        <v>0.4660171465183211</v>
+      </c>
+      <c r="AI10">
+        <v>0.2759540628594485</v>
+      </c>
+      <c r="AJ10">
+        <v>0.4207832322118036</v>
+      </c>
+      <c r="AK10">
+        <v>0.240847613876015</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bangkok Bank Public Company Limited (SET:BBL)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0669</v>
+      </c>
+      <c r="E11">
+        <v>0.0399</v>
+      </c>
+      <c r="F11">
+        <v>0.0738</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1350.4</v>
+      </c>
+      <c r="L11">
+        <v>0.3149033416505375</v>
+      </c>
+      <c r="M11">
+        <v>413.1</v>
+      </c>
+      <c r="N11">
+        <v>0.04919204067780464</v>
+      </c>
+      <c r="O11">
+        <v>0.3059093601895734</v>
+      </c>
+      <c r="P11">
+        <v>413.1</v>
+      </c>
+      <c r="Q11">
+        <v>0.04919204067780464</v>
+      </c>
+      <c r="R11">
+        <v>0.3059093601895734</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>1294</v>
+      </c>
+      <c r="V11">
+        <v>0.1540898103052026</v>
+      </c>
+      <c r="W11">
+        <v>0.09348692955250333</v>
+      </c>
+      <c r="X11">
+        <v>0.09223101877168847</v>
+      </c>
+      <c r="Y11">
+        <v>0.001255910780814856</v>
+      </c>
+      <c r="Z11">
+        <v>0.186730357236166</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.07474603985766179</v>
+      </c>
+      <c r="AC11">
+        <v>-0.07474603985766179</v>
+      </c>
+      <c r="AD11">
+        <v>8657</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>8657</v>
+      </c>
+      <c r="AG11">
+        <v>7363</v>
+      </c>
+      <c r="AH11">
+        <v>0.5076020100031077</v>
+      </c>
+      <c r="AI11">
+        <v>0.3370672771801131</v>
+      </c>
+      <c r="AJ11">
+        <v>0.467174681327606</v>
+      </c>
+      <c r="AK11">
+        <v>0.3018946833242447</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kasikornbank Public Company Limited (SET:KBANK)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0425</v>
+      </c>
+      <c r="E12">
+        <v>0.05139999999999999</v>
+      </c>
+      <c r="F12">
+        <v>0.053</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1468.6</v>
+      </c>
+      <c r="L12">
+        <v>0.3133213859020311</v>
+      </c>
+      <c r="M12">
+        <v>564.4</v>
+      </c>
+      <c r="N12">
+        <v>0.05257960537347915</v>
+      </c>
+      <c r="O12">
+        <v>0.3843115892686913</v>
+      </c>
+      <c r="P12">
+        <v>564.4</v>
+      </c>
+      <c r="Q12">
+        <v>0.05257960537347915</v>
+      </c>
+      <c r="R12">
+        <v>0.3843115892686913</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>1030.2</v>
+      </c>
+      <c r="V12">
+        <v>0.09597361703713364</v>
+      </c>
+      <c r="W12">
+        <v>0.1022417153996101</v>
+      </c>
+      <c r="X12">
+        <v>0.08761862812816236</v>
+      </c>
+      <c r="Y12">
+        <v>0.01462308727144777</v>
+      </c>
+      <c r="Z12">
+        <v>0.2089636079123701</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.07481891578725205</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07481891578725205</v>
+      </c>
+      <c r="AD12">
+        <v>8633.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>8633.5</v>
+      </c>
+      <c r="AG12">
+        <v>7603.3</v>
+      </c>
+      <c r="AH12">
+        <v>0.4457679538613258</v>
+      </c>
+      <c r="AI12">
+        <v>0.3109288790930176</v>
+      </c>
+      <c r="AJ12">
+        <v>0.4146312201772325</v>
+      </c>
+      <c r="AK12">
+        <v>0.2843779687768827</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Krung Thai Bank Public Company Limited (SET:KTB)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D13">
         <v>0.0463</v>
       </c>
-      <c r="E7">
+      <c r="E13">
         <v>0.0713</v>
       </c>
-      <c r="F7">
+      <c r="F13">
         <v>0.0673</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>0.0004944288922771767</v>
       </c>
-      <c r="J7">
+      <c r="J13">
         <v>0.0003978621429015742</v>
       </c>
-      <c r="K7">
+      <c r="K13">
         <v>1221.2</v>
       </c>
-      <c r="L7">
+      <c r="L13">
         <v>0.3213684210526316</v>
       </c>
-      <c r="M7">
+      <c r="M13">
         <v>375.1</v>
       </c>
-      <c r="N7">
+      <c r="N13">
         <v>0.04386621447783885</v>
       </c>
-      <c r="O7">
+      <c r="O13">
         <v>0.3071568948575172</v>
       </c>
-      <c r="P7">
+      <c r="P13">
         <v>375.1</v>
       </c>
-      <c r="Q7">
+      <c r="Q13">
         <v>0.04386621447783885</v>
       </c>
-      <c r="R7">
+      <c r="R13">
         <v>0.3071568948575172</v>
       </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>1633.6</v>
       </c>
-      <c r="V7">
+      <c r="V13">
         <v>0.1910419833937551</v>
       </c>
-      <c r="W7">
+      <c r="W13">
         <v>0.1141372413406359</v>
       </c>
-      <c r="X7">
-        <v>0.08699688799193377</v>
-      </c>
-      <c r="Y7">
-        <v>0.02714035334870217</v>
-      </c>
-      <c r="Z7">
+      <c r="X13">
+        <v>0.08698574170546927</v>
+      </c>
+      <c r="Y13">
+        <v>0.02715149963516666</v>
+      </c>
+      <c r="Z13">
         <v>0.227946466530073</v>
       </c>
-      <c r="AA7">
+      <c r="AA13">
         <v>9.06912696404968E-05</v>
       </c>
-      <c r="AB7">
-        <v>0.07544499135137808</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07535430008173759</v>
-      </c>
-      <c r="AD7">
+      <c r="AB13">
+        <v>0.07543870540898139</v>
+      </c>
+      <c r="AC13">
+        <v>-0.07534801413934089</v>
+      </c>
+      <c r="AD13">
         <v>6607.7</v>
       </c>
-      <c r="AE7">
+      <c r="AE13">
         <v>4.005851046733644</v>
       </c>
-      <c r="AF7">
+      <c r="AF13">
         <v>6611.705851046733</v>
       </c>
-      <c r="AG7">
+      <c r="AG13">
         <v>4978.105851046734</v>
       </c>
-      <c r="AH7">
+      <c r="AH13">
         <v>0.4360505252820891</v>
       </c>
-      <c r="AI7">
+      <c r="AI13">
         <v>0.322830802237682</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ13">
         <v>0.367955274048032</v>
       </c>
-      <c r="AK7">
+      <c r="AK13">
         <v>0.2641352540260956</v>
       </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
         <v>2465.559701492537</v>
       </c>
-      <c r="AP7">
+      <c r="AP13">
         <v>1857.502183226393</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Thai Credit Bank Public Company Limited (SET:CREDIT)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="L14">
+        <v>0.3309716599190283</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>13.5</v>
+      </c>
+      <c r="V14">
+        <v>0.0202854996243426</v>
+      </c>
+      <c r="W14">
+        <v>0.2134000435066347</v>
+      </c>
+      <c r="X14">
+        <v>0.09385071115858636</v>
+      </c>
+      <c r="Y14">
+        <v>0.1195493323480484</v>
+      </c>
+      <c r="Z14">
+        <v>0.252620813091281</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.07546335516678269</v>
+      </c>
+      <c r="AC14">
+        <v>-0.07546335516678269</v>
+      </c>
+      <c r="AD14">
+        <v>739</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>739</v>
+      </c>
+      <c r="AG14">
+        <v>725.5</v>
+      </c>
+      <c r="AH14">
+        <v>0.5261658953364187</v>
+      </c>
+      <c r="AI14">
+        <v>0.5222245777683556</v>
+      </c>
+      <c r="AJ14">
+        <v>0.5215672178289</v>
+      </c>
+      <c r="AK14">
+        <v>0.5176227168949772</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
